--- a/docs/QuickStay-Quan-Tri-Du-An.xlsx
+++ b/docs/QuickStay-Quan-Tri-Du-An.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="512">
   <si>
     <t>Dự án QuickStay – Hệ thống đặt phòng khách sạn trực tuyến</t>
   </si>
@@ -134,6 +134,12 @@
     <t>Proposal đã nộp</t>
   </si>
   <si>
+    <t>T030 · Tạo PR template và quy ước commit</t>
+  </si>
+  <si>
+    <t>PR template</t>
+  </si>
+  <si>
     <t>T019 · Họp daily, cập nhật bảng công việc</t>
   </si>
   <si>
@@ -146,12 +152,6 @@
     <t>README</t>
   </si>
   <si>
-    <t>T030 · Tạo PR template và quy ước commit</t>
-  </si>
-  <si>
-    <t>PR template</t>
-  </si>
-  <si>
     <t>T047 · Họp daily, cập nhật bảng công việc</t>
   </si>
   <si>
@@ -383,46 +383,64 @@
     <t>Backend chạy với MySQL</t>
   </si>
   <si>
+    <t>T027 · docker-compose: dịch vụ mysql có healthcheck và volume</t>
+  </si>
+  <si>
+    <t>MySQL lên bằng compose</t>
+  </si>
+  <si>
+    <t>T233 · Soạn .gitignore và cấu trúc thư mục repo (backend, frontend, docs)</t>
+  </si>
+  <si>
+    <t>Cấu trúc repo thống nhất</t>
+  </si>
+  <si>
+    <t>T025 · Khởi tạo React + Vite + Tailwind + Zustand + React Router</t>
+  </si>
+  <si>
+    <t>npm run dev chạy được</t>
+  </si>
+  <si>
+    <t>T026 · Dựng layout chung và khung Navbar</t>
+  </si>
+  <si>
+    <t>Layout, Navbar khung</t>
+  </si>
+  <si>
     <t>T014 · Viết Dockerfile backend (Gradle + JDK)</t>
   </si>
   <si>
     <t>Image backend build được</t>
   </si>
   <si>
-    <t>T015 · Viết Dockerfile frontend (Node build + Nginx) và nginx.conf</t>
+    <t>T041 · GitHub Actions: build và test backend khi push/PR</t>
+  </si>
+  <si>
+    <t>Job backend xanh</t>
+  </si>
+  <si>
+    <t>T234 · Viết nginx.conf: proxy /api sang backend và SPA fallback</t>
+  </si>
+  <si>
+    <t>nginx.conf</t>
+  </si>
+  <si>
+    <t>T015 · Viết Dockerfile frontend (Node build + Nginx)</t>
   </si>
   <si>
     <t>Image frontend build được</t>
   </si>
   <si>
-    <t>T025 · Khởi tạo React + Vite + Tailwind + Zustand + React Router</t>
-  </si>
-  <si>
-    <t>npm run dev chạy được</t>
-  </si>
-  <si>
-    <t>T026 · Dựng layout chung và khung Navbar</t>
-  </si>
-  <si>
-    <t>Layout, Navbar khung</t>
-  </si>
-  <si>
-    <t>T027 · docker-compose: dịch vụ mysql có healthcheck và volume</t>
-  </si>
-  <si>
-    <t>MySQL lên bằng compose</t>
-  </si>
-  <si>
     <t>T028 · docker-compose: backend, frontend, biến môi trường, .env.example</t>
   </si>
   <si>
     <t>docker compose up chạy cả hệ thống</t>
   </si>
   <si>
-    <t>T041 · GitHub Actions: build và test backend khi push/PR</t>
-  </si>
-  <si>
-    <t>Job backend xanh</t>
+    <t>T070 · Chạy thử toàn hệ thống bằng docker compose và ghi lỗi</t>
+  </si>
+  <si>
+    <t>Hệ thống chạy từ đầu</t>
   </si>
   <si>
     <t>T042 · GitHub Actions: build và test frontend</t>
@@ -431,12 +449,6 @@
     <t>Job frontend xanh</t>
   </si>
   <si>
-    <t>T070 · Chạy thử toàn hệ thống bằng docker compose và ghi lỗi</t>
-  </si>
-  <si>
-    <t>Hệ thống chạy từ đầu</t>
-  </si>
-  <si>
     <t>T071 · Logging SLF4J/Logback cho exception quan trọng</t>
   </si>
   <si>
@@ -545,18 +557,18 @@
     <t>Khách sạn &amp; Tìm kiếm (UC04–UC05)</t>
   </si>
   <si>
-    <t>T036 · Viết entity Hotel, Room và repository</t>
+    <t>T037 · Viết seed dữ liệu mẫu 4 khách sạn và các loại phòng</t>
+  </si>
+  <si>
+    <t>Dữ liệu mẫu tự tạo (UC04)</t>
+  </si>
+  <si>
+    <t>T036 · Viết entity Hotel, Room, Booking và repository</t>
   </si>
   <si>
     <t>Entity, repository (UC04, UC05)</t>
   </si>
   <si>
-    <t>T037 · Viết seed dữ liệu mẫu 4 khách sạn và các loại phòng</t>
-  </si>
-  <si>
-    <t>Dữ liệu mẫu tự tạo (UC04)</t>
-  </si>
-  <si>
     <t>T048 · API danh sách khách sạn kèm giá thấp nhất mỗi đêm</t>
   </si>
   <si>
@@ -653,24 +665,135 @@
     <t>Hết phòng khóa nút (UC05)</t>
   </si>
   <si>
+    <t>T165 · API phân trang danh sách khách sạn và đơn đặt phòng</t>
+  </si>
+  <si>
+    <t>Trang, kích thước trang (UC04, UC11)</t>
+  </si>
+  <si>
     <t>T153 · Tối ưu truy vấn phòng trống và thêm chỉ mục CSDL</t>
   </si>
   <si>
     <t>Truy vấn dưới 500 ms (UC05)</t>
   </si>
   <si>
-    <t>T165 · API phân trang danh sách khách sạn và đơn đặt phòng</t>
-  </si>
-  <si>
-    <t>Trang, kích thước trang (UC04, UC11)</t>
-  </si>
-  <si>
-    <t>T175 · Hỗ trợ Đức nối API phân trang ở giao diện</t>
+    <t>T236 · Giao diện phân trang danh sách khách sạn và đơn đặt phòng</t>
+  </si>
+  <si>
+    <t>Phân trang chạy được (UC04, UC11)</t>
+  </si>
+  <si>
+    <t>T175 · Kiểm thử phân trang qua API và giao diện, sửa lỗi nếu có</t>
   </si>
   <si>
     <t>Phân trang chạy đầu cuối (UC04, UC11)</t>
   </si>
   <si>
+    <t>Quản trị khách sạn/phòng/đơn (UC09–UC11)</t>
+  </si>
+  <si>
+    <t>T119 · Bộ xử lý lỗi chung: trả {"message"} thống nhất cho mọi lỗi</t>
+  </si>
+  <si>
+    <t>ApiExceptionHandler</t>
+  </si>
+  <si>
+    <t>T082 · API admin khách sạn: thêm (POST) và sửa (PUT) kèm validate</t>
+  </si>
+  <si>
+    <t>POST/PUT /admin/hotels (UC09)</t>
+  </si>
+  <si>
+    <t>T083 · API admin khách sạn: danh sách (GET) và xóa (DELETE), chặn khi có đơn</t>
+  </si>
+  <si>
+    <t>Xóa có đơn trả 409 (UC09)</t>
+  </si>
+  <si>
+    <t>T094 · API admin loại phòng: thêm (POST) và sửa (PUT) kèm validate</t>
+  </si>
+  <si>
+    <t>POST/PUT /admin/rooms (UC10)</t>
+  </si>
+  <si>
+    <t>T095 · API admin loại phòng: danh sách, xóa, chặn khi có đơn</t>
+  </si>
+  <si>
+    <t>Xóa có đơn trả 409 (UC10)</t>
+  </si>
+  <si>
+    <t>T106 · API admin: danh sách toàn bộ đơn đặt phòng</t>
+  </si>
+  <si>
+    <t>GET /admin/bookings (UC11)</t>
+  </si>
+  <si>
+    <t>T107 · API admin: đổi trạng thái đơn theo luồng hợp lệ</t>
+  </si>
+  <si>
+    <t>Bước sai trả 409 (UC11)</t>
+  </si>
+  <si>
+    <t>T108 · Test API admin: CRUD, luồng trạng thái, phân quyền</t>
+  </si>
+  <si>
+    <t>Test xanh (UC09, UC10, UC11)</t>
+  </si>
+  <si>
+    <t>T118 · Dashboard admin: khung 3 tab và điều hướng</t>
+  </si>
+  <si>
+    <t>Khung admin (UC09, UC10, UC11)</t>
+  </si>
+  <si>
+    <t>T120 · Test các mã lỗi 400, 404, 409</t>
+  </si>
+  <si>
+    <t>Test xanh</t>
+  </si>
+  <si>
+    <t>T129 · Admin tab Đặt phòng: bảng đơn và bộ lọc trạng thái</t>
+  </si>
+  <si>
+    <t>Bảng đơn (UC11)</t>
+  </si>
+  <si>
+    <t>T130 · Admin tab Đặt phòng: nút chuyển trạng thái kế tiếp và hủy</t>
+  </si>
+  <si>
+    <t>Đổi trạng thái chạy được (UC11)</t>
+  </si>
+  <si>
+    <t>T133 · Sửa lỗi backend admin theo cột Bug</t>
+  </si>
+  <si>
+    <t>Bug admin đã đóng</t>
+  </si>
+  <si>
+    <t>T143 · Admin tab Khách sạn: bảng danh sách và form thêm/sửa</t>
+  </si>
+  <si>
+    <t>CRUD khách sạn (UC09)</t>
+  </si>
+  <si>
+    <t>T144 · Admin tab Khách sạn: xóa, hộp thoại xác nhận, lỗi 409</t>
+  </si>
+  <si>
+    <t>Xóa an toàn (UC09)</t>
+  </si>
+  <si>
+    <t>T154 · Admin tab Phòng: bảng danh sách và form thêm/sửa</t>
+  </si>
+  <si>
+    <t>CRUD loại phòng (UC10)</t>
+  </si>
+  <si>
+    <t>T155 · Admin tab Phòng: kiểm tra giá, sức chứa, số lượng và xóa</t>
+  </si>
+  <si>
+    <t>Validate đúng (UC10)</t>
+  </si>
+  <si>
     <t>AI: mô tả &amp; chatbot (UC12–UC13)</t>
   </si>
   <si>
@@ -716,6 +839,24 @@
     <t>Bấm nút điền mô tả (UC12)</t>
   </si>
   <si>
+    <t>T139 · Thử AI thật với khóa API (nếu có) và ghi kết quả</t>
+  </si>
+  <si>
+    <t>Kết quả thử (UC12, UC13)</t>
+  </si>
+  <si>
+    <t>T148 · Widget chatbot: nút tròn và khung chat</t>
+  </si>
+  <si>
+    <t>Khung chat (UC13)</t>
+  </si>
+  <si>
+    <t>T149 · Widget chatbot: nối API, hiển thị tin nhắn, xử lý lỗi</t>
+  </si>
+  <si>
+    <t>Chat được trên mọi trang (UC13)</t>
+  </si>
+  <si>
     <t>T137 · Nút "Tạo mô tả bằng AI" ở form phòng</t>
   </si>
   <si>
@@ -725,129 +866,6 @@
     <t>Danh sách lỗi (UC12)</t>
   </si>
   <si>
-    <t>T139 · Thử AI thật với khóa API (nếu có) và ghi kết quả</t>
-  </si>
-  <si>
-    <t>Kết quả thử (UC12, UC13)</t>
-  </si>
-  <si>
-    <t>T148 · Widget chatbot: nút tròn và khung chat</t>
-  </si>
-  <si>
-    <t>Khung chat (UC13)</t>
-  </si>
-  <si>
-    <t>T149 · Widget chatbot: nối API, hiển thị tin nhắn, xử lý lỗi</t>
-  </si>
-  <si>
-    <t>Chat được trên mọi trang (UC13)</t>
-  </si>
-  <si>
-    <t>Quản trị khách sạn/phòng/đơn (UC09–UC11)</t>
-  </si>
-  <si>
-    <t>T082 · API admin khách sạn: thêm (POST) và sửa (PUT) kèm validate</t>
-  </si>
-  <si>
-    <t>POST/PUT /admin/hotels (UC09)</t>
-  </si>
-  <si>
-    <t>T083 · API admin khách sạn: danh sách (GET) và xóa (DELETE), chặn khi có đơn</t>
-  </si>
-  <si>
-    <t>Xóa có đơn trả 409 (UC09)</t>
-  </si>
-  <si>
-    <t>T094 · API admin loại phòng: thêm (POST) và sửa (PUT) kèm validate</t>
-  </si>
-  <si>
-    <t>POST/PUT /admin/rooms (UC10)</t>
-  </si>
-  <si>
-    <t>T095 · API admin loại phòng: danh sách, xóa, chặn khi có đơn</t>
-  </si>
-  <si>
-    <t>Xóa có đơn trả 409 (UC10)</t>
-  </si>
-  <si>
-    <t>T106 · API admin: danh sách toàn bộ đơn đặt phòng</t>
-  </si>
-  <si>
-    <t>GET /admin/bookings (UC11)</t>
-  </si>
-  <si>
-    <t>T107 · API admin: đổi trạng thái đơn theo luồng hợp lệ</t>
-  </si>
-  <si>
-    <t>Bước sai trả 409 (UC11)</t>
-  </si>
-  <si>
-    <t>T108 · Test API admin: CRUD, luồng trạng thái, phân quyền</t>
-  </si>
-  <si>
-    <t>Test xanh (UC09, UC10, UC11)</t>
-  </si>
-  <si>
-    <t>T118 · Dashboard admin: khung 3 tab và điều hướng</t>
-  </si>
-  <si>
-    <t>Khung admin (UC09, UC10, UC11)</t>
-  </si>
-  <si>
-    <t>T119 · Bộ xử lý lỗi chung: trả {"message"} thống nhất cho mọi lỗi</t>
-  </si>
-  <si>
-    <t>ApiExceptionHandler</t>
-  </si>
-  <si>
-    <t>T120 · Test các mã lỗi 400, 404, 409</t>
-  </si>
-  <si>
-    <t>Test xanh</t>
-  </si>
-  <si>
-    <t>T129 · Admin tab Đặt phòng: bảng đơn và bộ lọc trạng thái</t>
-  </si>
-  <si>
-    <t>Bảng đơn (UC11)</t>
-  </si>
-  <si>
-    <t>T130 · Admin tab Đặt phòng: nút chuyển trạng thái kế tiếp và hủy</t>
-  </si>
-  <si>
-    <t>Đổi trạng thái chạy được (UC11)</t>
-  </si>
-  <si>
-    <t>T133 · Sửa lỗi backend admin theo cột Bug</t>
-  </si>
-  <si>
-    <t>Bug admin đã đóng</t>
-  </si>
-  <si>
-    <t>T143 · Admin tab Khách sạn: bảng danh sách và form thêm/sửa</t>
-  </si>
-  <si>
-    <t>CRUD khách sạn (UC09)</t>
-  </si>
-  <si>
-    <t>T144 · Admin tab Khách sạn: xóa, hộp thoại xác nhận, lỗi 409</t>
-  </si>
-  <si>
-    <t>Xóa an toàn (UC09)</t>
-  </si>
-  <si>
-    <t>T154 · Admin tab Phòng: bảng danh sách và form thêm/sửa</t>
-  </si>
-  <si>
-    <t>CRUD loại phòng (UC10)</t>
-  </si>
-  <si>
-    <t>T155 · Admin tab Phòng: kiểm tra giá, sức chứa, số lượng và xóa</t>
-  </si>
-  <si>
-    <t>Validate đúng (UC10)</t>
-  </si>
-  <si>
     <t>Đặt phòng (UC06–UC08)</t>
   </si>
   <si>
@@ -1034,54 +1052,54 @@
     <t>Test xanh (UC01, UC02, UC03)</t>
   </si>
   <si>
+    <t>T142 · Đo độ phủ test và liệt kê phần chưa phủ</t>
+  </si>
+  <si>
+    <t>Báo cáo độ phủ</t>
+  </si>
+  <si>
+    <t>T151 · Bổ sung test: đặt phòng, lịch sử, hủy (nhánh lỗi)</t>
+  </si>
+  <si>
+    <t>Test xanh (UC06, UC07, UC08)</t>
+  </si>
+  <si>
+    <t>T152 · Bổ sung test: API admin và phân quyền</t>
+  </si>
+  <si>
+    <t>T159 · Chạy E2E toàn luồng trên bản docker compose</t>
+  </si>
+  <si>
+    <t>E2E đạt 100%</t>
+  </si>
+  <si>
+    <t>T160 · Kiểm thử tải 50 request đồng thời</t>
+  </si>
+  <si>
+    <t>Số liệu NFR-01, NFR-03</t>
+  </si>
+  <si>
+    <t>T161 · Đo Lighthouse (First Contentful Paint)</t>
+  </si>
+  <si>
+    <t>Số liệu NFR-02</t>
+  </si>
+  <si>
+    <t>T164 · Test đồng thời chống đặt trùng: nhiều yêu cầu cho phòng cuối</t>
+  </si>
+  <si>
+    <t>Chỉ 1 yêu cầu thành công (UC06)</t>
+  </si>
+  <si>
+    <t>T166 · Sửa lỗi QA phía backend</t>
+  </si>
+  <si>
     <t>T141 · Bổ sung test: khách sạn, tìm kiếm, phòng trống (nhánh lỗi)</t>
   </si>
   <si>
     <t>Test xanh (UC04, UC05)</t>
   </si>
   <si>
-    <t>T142 · Đo độ phủ test và liệt kê phần chưa phủ</t>
-  </si>
-  <si>
-    <t>Báo cáo độ phủ</t>
-  </si>
-  <si>
-    <t>T151 · Bổ sung test: đặt phòng, lịch sử, hủy (nhánh lỗi)</t>
-  </si>
-  <si>
-    <t>Test xanh (UC06, UC07, UC08)</t>
-  </si>
-  <si>
-    <t>T152 · Bổ sung test: API admin và phân quyền</t>
-  </si>
-  <si>
-    <t>T159 · Chạy E2E toàn luồng trên bản docker compose</t>
-  </si>
-  <si>
-    <t>E2E đạt 100%</t>
-  </si>
-  <si>
-    <t>T160 · Kiểm thử tải 50 request đồng thời</t>
-  </si>
-  <si>
-    <t>Số liệu NFR-01, NFR-03</t>
-  </si>
-  <si>
-    <t>T161 · Đo Lighthouse (First Contentful Paint)</t>
-  </si>
-  <si>
-    <t>Số liệu NFR-02</t>
-  </si>
-  <si>
-    <t>T164 · Test đồng thời chống đặt trùng: nhiều yêu cầu cho phòng cuối</t>
-  </si>
-  <si>
-    <t>Chỉ 1 yêu cầu thành công (UC06)</t>
-  </si>
-  <si>
-    <t>T166 · Sửa lỗi QA phía backend</t>
-  </si>
-  <si>
     <t>T167 · Responsive Trang chủ và Chi tiết khách sạn (mobile/tablet/desktop)</t>
   </si>
   <si>
@@ -1160,16 +1178,22 @@
     <t>Triển khai &amp; Bàn giao</t>
   </si>
   <si>
+    <t>T235 · README khung: giới thiệu, công nghệ, cấu trúc thư mục</t>
+  </si>
+  <si>
+    <t>README khung</t>
+  </si>
+  <si>
+    <t>T121 · Workflow đẩy Docker image lên GHCR khi push main</t>
+  </si>
+  <si>
+    <t>Workflow GHCR</t>
+  </si>
+  <si>
     <t>T069 · Rà soát bảo mật cấu hình: secret, biến môi trường, .gitignore</t>
   </si>
   <si>
     <t>Không có bí mật trong Git</t>
-  </si>
-  <si>
-    <t>T121 · Workflow đẩy Docker image lên GHCR khi push main</t>
-  </si>
-  <si>
-    <t>Workflow GHCR</t>
   </si>
   <si>
     <t>T134 · Chuẩn bị môi trường triển khai (VPS hoặc máy demo)</t>
@@ -2235,7 +2259,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN252"/>
+  <dimension ref="A1:AN256"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2872,7 +2896,7 @@
         <v>38</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>9</v>
@@ -2881,10 +2905,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="28">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="H14" s="28">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="I14" s="29">
         <f>NETWORKDAYS(G14,H14)</f>
@@ -2934,7 +2958,7 @@
         <v>40</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>9</v>
@@ -3005,10 +3029,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="28">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="H16" s="28">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="I16" s="29">
         <f>NETWORKDAYS(G16,H16)</f>
@@ -3055,7 +3079,7 @@
         <v>43</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" s="25" t="s">
         <v>8</v>
@@ -5734,22 +5758,22 @@
         <v>28</v>
       </c>
       <c r="F60" s="22">
-        <f>AVERAGE(F61:F161)</f>
+        <f>AVERAGE(F61:F164)</f>
       </c>
       <c r="G60" s="23">
-        <f>MIN(G61:G161)</f>
+        <f>MIN(G61:G164)</f>
       </c>
       <c r="H60" s="23">
-        <f>MAX(H61:H161)</f>
+        <f>MAX(H61:H164)</f>
       </c>
       <c r="I60" s="19">
         <f>NETWORKDAYS(G60,H60)</f>
       </c>
       <c r="J60" s="23">
-        <f>IF(COUNT(J61:J161)=0,"",MIN(J61:J161))</f>
+        <f>IF(COUNT(J61:J164)=0,"",MIN(J61:J164))</f>
       </c>
       <c r="K60" s="23">
-        <f>IF(COUNT(K61:K161)=0,"",MAX(K61:K161))</f>
+        <f>IF(COUNT(K61:K164)=0,"",MAX(K61:K164))</f>
       </c>
       <c r="L60" s="19">
         <f>IF(OR(J60="",K60=""),"",NETWORKDAYS(J60,K60))</f>
@@ -5800,22 +5824,22 @@
         <v>28</v>
       </c>
       <c r="F61" s="34">
-        <f>AVERAGE(F62:F72)</f>
+        <f>AVERAGE(F62:F74)</f>
       </c>
       <c r="G61" s="35">
-        <f>MIN(G62:G72)</f>
+        <f>MIN(G62:G74)</f>
       </c>
       <c r="H61" s="35">
-        <f>MAX(H62:H72)</f>
+        <f>MAX(H62:H74)</f>
       </c>
       <c r="I61" s="31">
         <f>NETWORKDAYS(G61,H61)</f>
       </c>
       <c r="J61" s="35">
-        <f>IF(COUNT(J62:J72)=0,"",MIN(J62:J72))</f>
+        <f>IF(COUNT(J62:J74)=0,"",MIN(J62:J74))</f>
       </c>
       <c r="K61" s="35">
-        <f>IF(COUNT(K62:K72)=0,"",MAX(K62:K72))</f>
+        <f>IF(COUNT(K62:K74)=0,"",MAX(K62:K74))</f>
       </c>
       <c r="L61" s="31">
         <f>IF(OR(J61="",K61=""),"",NETWORKDAYS(J61,K61))</f>
@@ -6303,10 +6327,10 @@
         <v>0</v>
       </c>
       <c r="G69" s="28">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="H69" s="28">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="I69" s="29">
         <f>NETWORKDAYS(G69,H69)</f>
@@ -6427,10 +6451,10 @@
         <v>0</v>
       </c>
       <c r="G71" s="28">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="H71" s="28">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="I71" s="29">
         <f>NETWORKDAYS(G71,H71)</f>
@@ -6531,96 +6555,92 @@
       <c r="AM72" s="30"/>
       <c r="AN72" s="30"/>
     </row>
-    <row r="73" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A73" s="31">
-        <v>2</v>
-      </c>
-      <c r="B73" s="32" t="s">
+    <row r="73" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A73" s="25">
+        <v>12</v>
+      </c>
+      <c r="B73" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="C73" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="D73" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="F73" s="34">
-        <f>AVERAGE(F74:F89)</f>
-      </c>
-      <c r="G73" s="35">
-        <f>MIN(G74:G89)</f>
-      </c>
-      <c r="H73" s="35">
-        <f>MAX(H74:H89)</f>
-      </c>
-      <c r="I73" s="31">
+      <c r="C73" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="27">
+        <v>0</v>
+      </c>
+      <c r="G73" s="28">
+        <v>46325</v>
+      </c>
+      <c r="H73" s="28">
+        <v>46325</v>
+      </c>
+      <c r="I73" s="29">
         <f>NETWORKDAYS(G73,H73)</f>
       </c>
-      <c r="J73" s="35">
-        <f>IF(COUNT(J74:J89)=0,"",MIN(J74:J89))</f>
-      </c>
-      <c r="K73" s="35">
-        <f>IF(COUNT(K74:K89)=0,"",MAX(K74:K89))</f>
-      </c>
-      <c r="L73" s="31">
+      <c r="J73" s="28"/>
+      <c r="K73" s="28"/>
+      <c r="L73" s="29">
         <f>IF(OR(J73="",K73=""),"",NETWORKDAYS(J73,K73))</f>
       </c>
-      <c r="M73" s="36"/>
-      <c r="N73" s="36"/>
-      <c r="O73" s="36"/>
-      <c r="P73" s="36"/>
-      <c r="Q73" s="36"/>
-      <c r="R73" s="36"/>
-      <c r="S73" s="36"/>
-      <c r="T73" s="36"/>
-      <c r="U73" s="36"/>
-      <c r="V73" s="36"/>
-      <c r="W73" s="36"/>
-      <c r="X73" s="36"/>
-      <c r="Y73" s="36"/>
-      <c r="Z73" s="36"/>
-      <c r="AA73" s="36"/>
-      <c r="AB73" s="36"/>
-      <c r="AC73" s="36"/>
-      <c r="AD73" s="36"/>
-      <c r="AE73" s="36"/>
-      <c r="AF73" s="36"/>
-      <c r="AG73" s="36"/>
-      <c r="AH73" s="36"/>
-      <c r="AI73" s="36"/>
-      <c r="AJ73" s="36"/>
-      <c r="AK73" s="36"/>
-      <c r="AL73" s="36"/>
-      <c r="AM73" s="36"/>
-      <c r="AN73" s="36"/>
+      <c r="M73" s="30"/>
+      <c r="N73" s="30"/>
+      <c r="O73" s="30"/>
+      <c r="P73" s="30"/>
+      <c r="Q73" s="30"/>
+      <c r="R73" s="30"/>
+      <c r="S73" s="30"/>
+      <c r="T73" s="30"/>
+      <c r="U73" s="30"/>
+      <c r="V73" s="30"/>
+      <c r="W73" s="30"/>
+      <c r="X73" s="30"/>
+      <c r="Y73" s="30"/>
+      <c r="Z73" s="30"/>
+      <c r="AA73" s="30"/>
+      <c r="AB73" s="30"/>
+      <c r="AC73" s="30"/>
+      <c r="AD73" s="30"/>
+      <c r="AE73" s="30"/>
+      <c r="AF73" s="30"/>
+      <c r="AG73" s="30"/>
+      <c r="AH73" s="30"/>
+      <c r="AI73" s="30"/>
+      <c r="AJ73" s="30"/>
+      <c r="AK73" s="30"/>
+      <c r="AL73" s="30"/>
+      <c r="AM73" s="30"/>
+      <c r="AN73" s="30"/>
     </row>
     <row r="74" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A74" s="25">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E74" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F74" s="27">
         <v>0</v>
       </c>
       <c r="G74" s="28">
-        <v>46322</v>
+        <v>46331</v>
       </c>
       <c r="H74" s="28">
-        <v>46322</v>
+        <v>46331</v>
       </c>
       <c r="I74" s="29">
         <f>NETWORKDAYS(G74,H74)</f>
@@ -6659,71 +6679,75 @@
       <c r="AM74" s="30"/>
       <c r="AN74" s="30"/>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A75" s="25">
+    <row r="75" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A75" s="31">
         <v>2</v>
       </c>
-      <c r="B75" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="C75" s="26" t="s">
+      <c r="B75" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="D75" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" s="27">
-        <v>0</v>
-      </c>
-      <c r="G75" s="28">
-        <v>46322</v>
-      </c>
-      <c r="H75" s="28">
-        <v>46322</v>
-      </c>
-      <c r="I75" s="29">
+      <c r="C75" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" s="34">
+        <f>AVERAGE(F76:F91)</f>
+      </c>
+      <c r="G75" s="35">
+        <f>MIN(G76:G91)</f>
+      </c>
+      <c r="H75" s="35">
+        <f>MAX(H76:H91)</f>
+      </c>
+      <c r="I75" s="31">
         <f>NETWORKDAYS(G75,H75)</f>
       </c>
-      <c r="J75" s="28"/>
-      <c r="K75" s="28"/>
-      <c r="L75" s="29">
+      <c r="J75" s="35">
+        <f>IF(COUNT(J76:J91)=0,"",MIN(J76:J91))</f>
+      </c>
+      <c r="K75" s="35">
+        <f>IF(COUNT(K76:K91)=0,"",MAX(K76:K91))</f>
+      </c>
+      <c r="L75" s="31">
         <f>IF(OR(J75="",K75=""),"",NETWORKDAYS(J75,K75))</f>
       </c>
-      <c r="M75" s="30"/>
-      <c r="N75" s="30"/>
-      <c r="O75" s="30"/>
-      <c r="P75" s="30"/>
-      <c r="Q75" s="30"/>
-      <c r="R75" s="30"/>
-      <c r="S75" s="30"/>
-      <c r="T75" s="30"/>
-      <c r="U75" s="30"/>
-      <c r="V75" s="30"/>
-      <c r="W75" s="30"/>
-      <c r="X75" s="30"/>
-      <c r="Y75" s="30"/>
-      <c r="Z75" s="30"/>
-      <c r="AA75" s="30"/>
-      <c r="AB75" s="30"/>
-      <c r="AC75" s="30"/>
-      <c r="AD75" s="30"/>
-      <c r="AE75" s="30"/>
-      <c r="AF75" s="30"/>
-      <c r="AG75" s="30"/>
-      <c r="AH75" s="30"/>
-      <c r="AI75" s="30"/>
-      <c r="AJ75" s="30"/>
-      <c r="AK75" s="30"/>
-      <c r="AL75" s="30"/>
-      <c r="AM75" s="30"/>
-      <c r="AN75" s="30"/>
+      <c r="M75" s="36"/>
+      <c r="N75" s="36"/>
+      <c r="O75" s="36"/>
+      <c r="P75" s="36"/>
+      <c r="Q75" s="36"/>
+      <c r="R75" s="36"/>
+      <c r="S75" s="36"/>
+      <c r="T75" s="36"/>
+      <c r="U75" s="36"/>
+      <c r="V75" s="36"/>
+      <c r="W75" s="36"/>
+      <c r="X75" s="36"/>
+      <c r="Y75" s="36"/>
+      <c r="Z75" s="36"/>
+      <c r="AA75" s="36"/>
+      <c r="AB75" s="36"/>
+      <c r="AC75" s="36"/>
+      <c r="AD75" s="36"/>
+      <c r="AE75" s="36"/>
+      <c r="AF75" s="36"/>
+      <c r="AG75" s="36"/>
+      <c r="AH75" s="36"/>
+      <c r="AI75" s="36"/>
+      <c r="AJ75" s="36"/>
+      <c r="AK75" s="36"/>
+      <c r="AL75" s="36"/>
+      <c r="AM75" s="36"/>
+      <c r="AN75" s="36"/>
     </row>
     <row r="76" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A76" s="25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B76" s="26" t="s">
         <v>145</v>
@@ -6785,7 +6809,7 @@
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A77" s="25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B77" s="26" t="s">
         <v>147</v>
@@ -6803,10 +6827,10 @@
         <v>0</v>
       </c>
       <c r="G77" s="28">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="H77" s="28">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="I77" s="29">
         <f>NETWORKDAYS(G77,H77)</f>
@@ -6847,7 +6871,7 @@
     </row>
     <row r="78" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A78" s="25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B78" s="26" t="s">
         <v>149</v>
@@ -6856,19 +6880,19 @@
         <v>150</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E78" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F78" s="27">
         <v>0</v>
       </c>
       <c r="G78" s="28">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="H78" s="28">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="I78" s="29">
         <f>NETWORKDAYS(G78,H78)</f>
@@ -6909,7 +6933,7 @@
     </row>
     <row r="79" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A79" s="25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B79" s="26" t="s">
         <v>151</v>
@@ -6918,10 +6942,10 @@
         <v>152</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E79" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F79" s="27">
         <v>0</v>
@@ -6971,7 +6995,7 @@
     </row>
     <row r="80" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A80" s="25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B80" s="26" t="s">
         <v>153</v>
@@ -7033,7 +7057,7 @@
     </row>
     <row r="81" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A81" s="25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B81" s="26" t="s">
         <v>155</v>
@@ -7042,10 +7066,10 @@
         <v>156</v>
       </c>
       <c r="D81" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E81" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F81" s="27">
         <v>0</v>
@@ -7095,7 +7119,7 @@
     </row>
     <row r="82" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A82" s="25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B82" s="26" t="s">
         <v>157</v>
@@ -7113,10 +7137,10 @@
         <v>0</v>
       </c>
       <c r="G82" s="28">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="H82" s="28">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="I82" s="29">
         <f>NETWORKDAYS(G82,H82)</f>
@@ -7157,7 +7181,7 @@
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A83" s="25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B83" s="26" t="s">
         <v>159</v>
@@ -7166,19 +7190,19 @@
         <v>160</v>
       </c>
       <c r="D83" s="25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E83" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F83" s="27">
         <v>0</v>
       </c>
       <c r="G83" s="28">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="H83" s="28">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="I83" s="29">
         <f>NETWORKDAYS(G83,H83)</f>
@@ -7219,7 +7243,7 @@
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A84" s="25">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B84" s="26" t="s">
         <v>161</v>
@@ -7228,10 +7252,10 @@
         <v>162</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E84" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F84" s="27">
         <v>0</v>
@@ -7281,7 +7305,7 @@
     </row>
     <row r="85" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A85" s="25">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B85" s="26" t="s">
         <v>163</v>
@@ -7290,10 +7314,10 @@
         <v>164</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E85" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F85" s="27">
         <v>0</v>
@@ -7343,7 +7367,7 @@
     </row>
     <row r="86" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A86" s="25">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B86" s="26" t="s">
         <v>165</v>
@@ -7352,19 +7376,19 @@
         <v>166</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E86" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F86" s="27">
         <v>0</v>
       </c>
       <c r="G86" s="28">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="H86" s="28">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="I86" s="29">
         <f>NETWORKDAYS(G86,H86)</f>
@@ -7405,7 +7429,7 @@
     </row>
     <row r="87" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A87" s="25">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B87" s="26" t="s">
         <v>167</v>
@@ -7414,19 +7438,19 @@
         <v>168</v>
       </c>
       <c r="D87" s="25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F87" s="27">
         <v>0</v>
       </c>
       <c r="G87" s="28">
-        <v>46331</v>
+        <v>46324</v>
       </c>
       <c r="H87" s="28">
-        <v>46331</v>
+        <v>46324</v>
       </c>
       <c r="I87" s="29">
         <f>NETWORKDAYS(G87,H87)</f>
@@ -7467,7 +7491,7 @@
     </row>
     <row r="88" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A88" s="25">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B88" s="26" t="s">
         <v>169</v>
@@ -7476,19 +7500,19 @@
         <v>170</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F88" s="27">
         <v>0</v>
       </c>
       <c r="G88" s="28">
-        <v>46331</v>
+        <v>46325</v>
       </c>
       <c r="H88" s="28">
-        <v>46331</v>
+        <v>46325</v>
       </c>
       <c r="I88" s="29">
         <f>NETWORKDAYS(G88,H88)</f>
@@ -7529,7 +7553,7 @@
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A89" s="25">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B89" s="26" t="s">
         <v>171</v>
@@ -7538,19 +7562,19 @@
         <v>172</v>
       </c>
       <c r="D89" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E89" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F89" s="27">
         <v>0</v>
       </c>
       <c r="G89" s="28">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="H89" s="28">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="I89" s="29">
         <f>NETWORKDAYS(G89,H89)</f>
@@ -7589,81 +7613,77 @@
       <c r="AM89" s="30"/>
       <c r="AN89" s="30"/>
     </row>
-    <row r="90" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A90" s="31">
-        <v>3</v>
-      </c>
-      <c r="B90" s="32" t="s">
+    <row r="90" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A90" s="25">
+        <v>15</v>
+      </c>
+      <c r="B90" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C90" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="D90" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="E90" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="F90" s="34">
-        <f>AVERAGE(F91:F111)</f>
-      </c>
-      <c r="G90" s="35">
-        <f>MIN(G91:G111)</f>
-      </c>
-      <c r="H90" s="35">
-        <f>MAX(H91:H111)</f>
-      </c>
-      <c r="I90" s="31">
+      <c r="C90" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="D90" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" s="27">
+        <v>0</v>
+      </c>
+      <c r="G90" s="28">
+        <v>46331</v>
+      </c>
+      <c r="H90" s="28">
+        <v>46331</v>
+      </c>
+      <c r="I90" s="29">
         <f>NETWORKDAYS(G90,H90)</f>
       </c>
-      <c r="J90" s="35">
-        <f>IF(COUNT(J91:J111)=0,"",MIN(J91:J111))</f>
-      </c>
-      <c r="K90" s="35">
-        <f>IF(COUNT(K91:K111)=0,"",MAX(K91:K111))</f>
-      </c>
-      <c r="L90" s="31">
+      <c r="J90" s="28"/>
+      <c r="K90" s="28"/>
+      <c r="L90" s="29">
         <f>IF(OR(J90="",K90=""),"",NETWORKDAYS(J90,K90))</f>
       </c>
-      <c r="M90" s="36"/>
-      <c r="N90" s="36"/>
-      <c r="O90" s="36"/>
-      <c r="P90" s="36"/>
-      <c r="Q90" s="36"/>
-      <c r="R90" s="36"/>
-      <c r="S90" s="36"/>
-      <c r="T90" s="36"/>
-      <c r="U90" s="36"/>
-      <c r="V90" s="36"/>
-      <c r="W90" s="36"/>
-      <c r="X90" s="36"/>
-      <c r="Y90" s="36"/>
-      <c r="Z90" s="36"/>
-      <c r="AA90" s="36"/>
-      <c r="AB90" s="36"/>
-      <c r="AC90" s="36"/>
-      <c r="AD90" s="36"/>
-      <c r="AE90" s="36"/>
-      <c r="AF90" s="36"/>
-      <c r="AG90" s="36"/>
-      <c r="AH90" s="36"/>
-      <c r="AI90" s="36"/>
-      <c r="AJ90" s="36"/>
-      <c r="AK90" s="36"/>
-      <c r="AL90" s="36"/>
-      <c r="AM90" s="36"/>
-      <c r="AN90" s="36"/>
+      <c r="M90" s="30"/>
+      <c r="N90" s="30"/>
+      <c r="O90" s="30"/>
+      <c r="P90" s="30"/>
+      <c r="Q90" s="30"/>
+      <c r="R90" s="30"/>
+      <c r="S90" s="30"/>
+      <c r="T90" s="30"/>
+      <c r="U90" s="30"/>
+      <c r="V90" s="30"/>
+      <c r="W90" s="30"/>
+      <c r="X90" s="30"/>
+      <c r="Y90" s="30"/>
+      <c r="Z90" s="30"/>
+      <c r="AA90" s="30"/>
+      <c r="AB90" s="30"/>
+      <c r="AC90" s="30"/>
+      <c r="AD90" s="30"/>
+      <c r="AE90" s="30"/>
+      <c r="AF90" s="30"/>
+      <c r="AG90" s="30"/>
+      <c r="AH90" s="30"/>
+      <c r="AI90" s="30"/>
+      <c r="AJ90" s="30"/>
+      <c r="AK90" s="30"/>
+      <c r="AL90" s="30"/>
+      <c r="AM90" s="30"/>
+      <c r="AN90" s="30"/>
     </row>
     <row r="91" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A91" s="25">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D91" s="25" t="s">
         <v>9</v>
@@ -7675,10 +7695,10 @@
         <v>0</v>
       </c>
       <c r="G91" s="28">
-        <v>46323</v>
+        <v>46332</v>
       </c>
       <c r="H91" s="28">
-        <v>46323</v>
+        <v>46332</v>
       </c>
       <c r="I91" s="29">
         <f>NETWORKDAYS(G91,H91)</f>
@@ -7717,71 +7737,75 @@
       <c r="AM91" s="30"/>
       <c r="AN91" s="30"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A92" s="25">
-        <v>2</v>
-      </c>
-      <c r="B92" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="C92" s="26" t="s">
+    <row r="92" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A92" s="31">
+        <v>3</v>
+      </c>
+      <c r="B92" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="D92" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E92" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" s="27">
-        <v>0</v>
-      </c>
-      <c r="G92" s="28">
-        <v>46323</v>
-      </c>
-      <c r="H92" s="28">
-        <v>46323</v>
-      </c>
-      <c r="I92" s="29">
+      <c r="C92" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="D92" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E92" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F92" s="34">
+        <f>AVERAGE(F93:F114)</f>
+      </c>
+      <c r="G92" s="35">
+        <f>MIN(G93:G114)</f>
+      </c>
+      <c r="H92" s="35">
+        <f>MAX(H93:H114)</f>
+      </c>
+      <c r="I92" s="31">
         <f>NETWORKDAYS(G92,H92)</f>
       </c>
-      <c r="J92" s="28"/>
-      <c r="K92" s="28"/>
-      <c r="L92" s="29">
+      <c r="J92" s="35">
+        <f>IF(COUNT(J93:J114)=0,"",MIN(J93:J114))</f>
+      </c>
+      <c r="K92" s="35">
+        <f>IF(COUNT(K93:K114)=0,"",MAX(K93:K114))</f>
+      </c>
+      <c r="L92" s="31">
         <f>IF(OR(J92="",K92=""),"",NETWORKDAYS(J92,K92))</f>
       </c>
-      <c r="M92" s="30"/>
-      <c r="N92" s="30"/>
-      <c r="O92" s="30"/>
-      <c r="P92" s="30"/>
-      <c r="Q92" s="30"/>
-      <c r="R92" s="30"/>
-      <c r="S92" s="30"/>
-      <c r="T92" s="30"/>
-      <c r="U92" s="30"/>
-      <c r="V92" s="30"/>
-      <c r="W92" s="30"/>
-      <c r="X92" s="30"/>
-      <c r="Y92" s="30"/>
-      <c r="Z92" s="30"/>
-      <c r="AA92" s="30"/>
-      <c r="AB92" s="30"/>
-      <c r="AC92" s="30"/>
-      <c r="AD92" s="30"/>
-      <c r="AE92" s="30"/>
-      <c r="AF92" s="30"/>
-      <c r="AG92" s="30"/>
-      <c r="AH92" s="30"/>
-      <c r="AI92" s="30"/>
-      <c r="AJ92" s="30"/>
-      <c r="AK92" s="30"/>
-      <c r="AL92" s="30"/>
-      <c r="AM92" s="30"/>
-      <c r="AN92" s="30"/>
+      <c r="M92" s="36"/>
+      <c r="N92" s="36"/>
+      <c r="O92" s="36"/>
+      <c r="P92" s="36"/>
+      <c r="Q92" s="36"/>
+      <c r="R92" s="36"/>
+      <c r="S92" s="36"/>
+      <c r="T92" s="36"/>
+      <c r="U92" s="36"/>
+      <c r="V92" s="36"/>
+      <c r="W92" s="36"/>
+      <c r="X92" s="36"/>
+      <c r="Y92" s="36"/>
+      <c r="Z92" s="36"/>
+      <c r="AA92" s="36"/>
+      <c r="AB92" s="36"/>
+      <c r="AC92" s="36"/>
+      <c r="AD92" s="36"/>
+      <c r="AE92" s="36"/>
+      <c r="AF92" s="36"/>
+      <c r="AG92" s="36"/>
+      <c r="AH92" s="36"/>
+      <c r="AI92" s="36"/>
+      <c r="AJ92" s="36"/>
+      <c r="AK92" s="36"/>
+      <c r="AL92" s="36"/>
+      <c r="AM92" s="36"/>
+      <c r="AN92" s="36"/>
     </row>
     <row r="93" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A93" s="25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>178</v>
@@ -7799,10 +7823,10 @@
         <v>0</v>
       </c>
       <c r="G93" s="28">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="H93" s="28">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="I93" s="29">
         <f>NETWORKDAYS(G93,H93)</f>
@@ -7843,7 +7867,7 @@
     </row>
     <row r="94" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A94" s="25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B94" s="26" t="s">
         <v>180</v>
@@ -7861,10 +7885,10 @@
         <v>0</v>
       </c>
       <c r="G94" s="28">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="H94" s="28">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="I94" s="29">
         <f>NETWORKDAYS(G94,H94)</f>
@@ -7905,7 +7929,7 @@
     </row>
     <row r="95" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A95" s="25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>182</v>
@@ -7967,7 +7991,7 @@
     </row>
     <row r="96" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A96" s="25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B96" s="26" t="s">
         <v>184</v>
@@ -7976,10 +8000,10 @@
         <v>185</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E96" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F96" s="27">
         <v>0</v>
@@ -8029,7 +8053,7 @@
     </row>
     <row r="97" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A97" s="25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>186</v>
@@ -8047,10 +8071,10 @@
         <v>0</v>
       </c>
       <c r="G97" s="28">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="H97" s="28">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="I97" s="29">
         <f>NETWORKDAYS(G97,H97)</f>
@@ -8091,7 +8115,7 @@
     </row>
     <row r="98" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A98" s="25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B98" s="26" t="s">
         <v>188</v>
@@ -8100,19 +8124,19 @@
         <v>189</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E98" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F98" s="27">
         <v>0</v>
       </c>
       <c r="G98" s="28">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="H98" s="28">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="I98" s="29">
         <f>NETWORKDAYS(G98,H98)</f>
@@ -8153,7 +8177,7 @@
     </row>
     <row r="99" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A99" s="25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>190</v>
@@ -8162,10 +8186,10 @@
         <v>191</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E99" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F99" s="27">
         <v>0</v>
@@ -8215,7 +8239,7 @@
     </row>
     <row r="100" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A100" s="25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B100" s="26" t="s">
         <v>192</v>
@@ -8224,10 +8248,10 @@
         <v>193</v>
       </c>
       <c r="D100" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E100" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F100" s="27">
         <v>0</v>
@@ -8277,7 +8301,7 @@
     </row>
     <row r="101" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A101" s="25">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>194</v>
@@ -8339,7 +8363,7 @@
     </row>
     <row r="102" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A102" s="25">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B102" s="26" t="s">
         <v>196</v>
@@ -8348,19 +8372,19 @@
         <v>197</v>
       </c>
       <c r="D102" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E102" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F102" s="27">
         <v>0</v>
       </c>
       <c r="G102" s="28">
-        <v>46328</v>
+        <v>46325</v>
       </c>
       <c r="H102" s="28">
-        <v>46328</v>
+        <v>46325</v>
       </c>
       <c r="I102" s="29">
         <f>NETWORKDAYS(G102,H102)</f>
@@ -8401,7 +8425,7 @@
     </row>
     <row r="103" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A103" s="25">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B103" s="26" t="s">
         <v>198</v>
@@ -8410,19 +8434,19 @@
         <v>199</v>
       </c>
       <c r="D103" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E103" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F103" s="27">
         <v>0</v>
       </c>
       <c r="G103" s="28">
-        <v>46328</v>
+        <v>46325</v>
       </c>
       <c r="H103" s="28">
-        <v>46328</v>
+        <v>46325</v>
       </c>
       <c r="I103" s="29">
         <f>NETWORKDAYS(G103,H103)</f>
@@ -8463,7 +8487,7 @@
     </row>
     <row r="104" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A104" s="25">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B104" s="26" t="s">
         <v>200</v>
@@ -8525,7 +8549,7 @@
     </row>
     <row r="105" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A105" s="25">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B105" s="26" t="s">
         <v>202</v>
@@ -8534,10 +8558,10 @@
         <v>203</v>
       </c>
       <c r="D105" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F105" s="27">
         <v>0</v>
@@ -8587,7 +8611,7 @@
     </row>
     <row r="106" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A106" s="25">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B106" s="26" t="s">
         <v>204</v>
@@ -8596,10 +8620,10 @@
         <v>205</v>
       </c>
       <c r="D106" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E106" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F106" s="27">
         <v>0</v>
@@ -8649,7 +8673,7 @@
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A107" s="25">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B107" s="26" t="s">
         <v>206</v>
@@ -8711,7 +8735,7 @@
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A108" s="25">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B108" s="26" t="s">
         <v>208</v>
@@ -8729,10 +8753,10 @@
         <v>0</v>
       </c>
       <c r="G108" s="28">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="H108" s="28">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="I108" s="29">
         <f>NETWORKDAYS(G108,H108)</f>
@@ -8773,7 +8797,7 @@
     </row>
     <row r="109" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A109" s="25">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B109" s="26" t="s">
         <v>210</v>
@@ -8782,19 +8806,19 @@
         <v>211</v>
       </c>
       <c r="D109" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E109" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F109" s="27">
         <v>0</v>
       </c>
       <c r="G109" s="28">
-        <v>46336</v>
+        <v>46328</v>
       </c>
       <c r="H109" s="28">
-        <v>46336</v>
+        <v>46328</v>
       </c>
       <c r="I109" s="29">
         <f>NETWORKDAYS(G109,H109)</f>
@@ -8835,7 +8859,7 @@
     </row>
     <row r="110" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A110" s="25">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B110" s="26" t="s">
         <v>212</v>
@@ -8844,19 +8868,19 @@
         <v>213</v>
       </c>
       <c r="D110" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E110" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F110" s="27">
         <v>0</v>
       </c>
       <c r="G110" s="28">
-        <v>46337</v>
+        <v>46329</v>
       </c>
       <c r="H110" s="28">
-        <v>46337</v>
+        <v>46329</v>
       </c>
       <c r="I110" s="29">
         <f>NETWORKDAYS(G110,H110)</f>
@@ -8897,7 +8921,7 @@
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A111" s="25">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B111" s="26" t="s">
         <v>214</v>
@@ -8915,10 +8939,10 @@
         <v>0</v>
       </c>
       <c r="G111" s="28">
-        <v>46338</v>
+        <v>46335</v>
       </c>
       <c r="H111" s="28">
-        <v>46338</v>
+        <v>46335</v>
       </c>
       <c r="I111" s="29">
         <f>NETWORKDAYS(G111,H111)</f>
@@ -8957,96 +8981,92 @@
       <c r="AM111" s="30"/>
       <c r="AN111" s="30"/>
     </row>
-    <row r="112" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A112" s="31">
-        <v>4</v>
-      </c>
-      <c r="B112" s="32" t="s">
+    <row r="112" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A112" s="25">
+        <v>20</v>
+      </c>
+      <c r="B112" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="C112" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="D112" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="E112" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="F112" s="34">
-        <f>AVERAGE(F113:F124)</f>
-      </c>
-      <c r="G112" s="35">
-        <f>MIN(G113:G124)</f>
-      </c>
-      <c r="H112" s="35">
-        <f>MAX(H113:H124)</f>
-      </c>
-      <c r="I112" s="31">
+      <c r="C112" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="D112" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="27">
+        <v>0</v>
+      </c>
+      <c r="G112" s="28">
+        <v>46336</v>
+      </c>
+      <c r="H112" s="28">
+        <v>46336</v>
+      </c>
+      <c r="I112" s="29">
         <f>NETWORKDAYS(G112,H112)</f>
       </c>
-      <c r="J112" s="35">
-        <f>IF(COUNT(J113:J124)=0,"",MIN(J113:J124))</f>
-      </c>
-      <c r="K112" s="35">
-        <f>IF(COUNT(K113:K124)=0,"",MAX(K113:K124))</f>
-      </c>
-      <c r="L112" s="31">
+      <c r="J112" s="28"/>
+      <c r="K112" s="28"/>
+      <c r="L112" s="29">
         <f>IF(OR(J112="",K112=""),"",NETWORKDAYS(J112,K112))</f>
       </c>
-      <c r="M112" s="36"/>
-      <c r="N112" s="36"/>
-      <c r="O112" s="36"/>
-      <c r="P112" s="36"/>
-      <c r="Q112" s="36"/>
-      <c r="R112" s="36"/>
-      <c r="S112" s="36"/>
-      <c r="T112" s="36"/>
-      <c r="U112" s="36"/>
-      <c r="V112" s="36"/>
-      <c r="W112" s="36"/>
-      <c r="X112" s="36"/>
-      <c r="Y112" s="36"/>
-      <c r="Z112" s="36"/>
-      <c r="AA112" s="36"/>
-      <c r="AB112" s="36"/>
-      <c r="AC112" s="36"/>
-      <c r="AD112" s="36"/>
-      <c r="AE112" s="36"/>
-      <c r="AF112" s="36"/>
-      <c r="AG112" s="36"/>
-      <c r="AH112" s="36"/>
-      <c r="AI112" s="36"/>
-      <c r="AJ112" s="36"/>
-      <c r="AK112" s="36"/>
-      <c r="AL112" s="36"/>
-      <c r="AM112" s="36"/>
-      <c r="AN112" s="36"/>
+      <c r="M112" s="30"/>
+      <c r="N112" s="30"/>
+      <c r="O112" s="30"/>
+      <c r="P112" s="30"/>
+      <c r="Q112" s="30"/>
+      <c r="R112" s="30"/>
+      <c r="S112" s="30"/>
+      <c r="T112" s="30"/>
+      <c r="U112" s="30"/>
+      <c r="V112" s="30"/>
+      <c r="W112" s="30"/>
+      <c r="X112" s="30"/>
+      <c r="Y112" s="30"/>
+      <c r="Z112" s="30"/>
+      <c r="AA112" s="30"/>
+      <c r="AB112" s="30"/>
+      <c r="AC112" s="30"/>
+      <c r="AD112" s="30"/>
+      <c r="AE112" s="30"/>
+      <c r="AF112" s="30"/>
+      <c r="AG112" s="30"/>
+      <c r="AH112" s="30"/>
+      <c r="AI112" s="30"/>
+      <c r="AJ112" s="30"/>
+      <c r="AK112" s="30"/>
+      <c r="AL112" s="30"/>
+      <c r="AM112" s="30"/>
+      <c r="AN112" s="30"/>
     </row>
     <row r="113" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A113" s="25">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B113" s="26" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C113" s="26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D113" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E113" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E113" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="F113" s="27">
         <v>0</v>
       </c>
       <c r="G113" s="28">
-        <v>46328</v>
+        <v>46336</v>
       </c>
       <c r="H113" s="28">
-        <v>46328</v>
+        <v>46336</v>
       </c>
       <c r="I113" s="29">
         <f>NETWORKDAYS(G113,H113)</f>
@@ -9087,28 +9107,28 @@
     </row>
     <row r="114" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A114" s="25">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B114" s="26" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C114" s="26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E114" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F114" s="27">
         <v>0</v>
       </c>
       <c r="G114" s="28">
-        <v>46328</v>
+        <v>46338</v>
       </c>
       <c r="H114" s="28">
-        <v>46328</v>
+        <v>46338</v>
       </c>
       <c r="I114" s="29">
         <f>NETWORKDAYS(G114,H114)</f>
@@ -9147,71 +9167,75 @@
       <c r="AM114" s="30"/>
       <c r="AN114" s="30"/>
     </row>
-    <row r="115" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A115" s="25">
-        <v>3</v>
-      </c>
-      <c r="B115" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="C115" s="26" t="s">
+    <row r="115" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A115" s="31">
+        <v>4</v>
+      </c>
+      <c r="B115" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="D115" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E115" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F115" s="27">
-        <v>0</v>
-      </c>
-      <c r="G115" s="28">
-        <v>46328</v>
-      </c>
-      <c r="H115" s="28">
-        <v>46328</v>
-      </c>
-      <c r="I115" s="29">
+      <c r="C115" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="D115" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E115" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F115" s="34">
+        <f>AVERAGE(F116:F132)</f>
+      </c>
+      <c r="G115" s="35">
+        <f>MIN(G116:G132)</f>
+      </c>
+      <c r="H115" s="35">
+        <f>MAX(H116:H132)</f>
+      </c>
+      <c r="I115" s="31">
         <f>NETWORKDAYS(G115,H115)</f>
       </c>
-      <c r="J115" s="28"/>
-      <c r="K115" s="28"/>
-      <c r="L115" s="29">
+      <c r="J115" s="35">
+        <f>IF(COUNT(J116:J132)=0,"",MIN(J116:J132))</f>
+      </c>
+      <c r="K115" s="35">
+        <f>IF(COUNT(K116:K132)=0,"",MAX(K116:K132))</f>
+      </c>
+      <c r="L115" s="31">
         <f>IF(OR(J115="",K115=""),"",NETWORKDAYS(J115,K115))</f>
       </c>
-      <c r="M115" s="30"/>
-      <c r="N115" s="30"/>
-      <c r="O115" s="30"/>
-      <c r="P115" s="30"/>
-      <c r="Q115" s="30"/>
-      <c r="R115" s="30"/>
-      <c r="S115" s="30"/>
-      <c r="T115" s="30"/>
-      <c r="U115" s="30"/>
-      <c r="V115" s="30"/>
-      <c r="W115" s="30"/>
-      <c r="X115" s="30"/>
-      <c r="Y115" s="30"/>
-      <c r="Z115" s="30"/>
-      <c r="AA115" s="30"/>
-      <c r="AB115" s="30"/>
-      <c r="AC115" s="30"/>
-      <c r="AD115" s="30"/>
-      <c r="AE115" s="30"/>
-      <c r="AF115" s="30"/>
-      <c r="AG115" s="30"/>
-      <c r="AH115" s="30"/>
-      <c r="AI115" s="30"/>
-      <c r="AJ115" s="30"/>
-      <c r="AK115" s="30"/>
-      <c r="AL115" s="30"/>
-      <c r="AM115" s="30"/>
-      <c r="AN115" s="30"/>
+      <c r="M115" s="36"/>
+      <c r="N115" s="36"/>
+      <c r="O115" s="36"/>
+      <c r="P115" s="36"/>
+      <c r="Q115" s="36"/>
+      <c r="R115" s="36"/>
+      <c r="S115" s="36"/>
+      <c r="T115" s="36"/>
+      <c r="U115" s="36"/>
+      <c r="V115" s="36"/>
+      <c r="W115" s="36"/>
+      <c r="X115" s="36"/>
+      <c r="Y115" s="36"/>
+      <c r="Z115" s="36"/>
+      <c r="AA115" s="36"/>
+      <c r="AB115" s="36"/>
+      <c r="AC115" s="36"/>
+      <c r="AD115" s="36"/>
+      <c r="AE115" s="36"/>
+      <c r="AF115" s="36"/>
+      <c r="AG115" s="36"/>
+      <c r="AH115" s="36"/>
+      <c r="AI115" s="36"/>
+      <c r="AJ115" s="36"/>
+      <c r="AK115" s="36"/>
+      <c r="AL115" s="36"/>
+      <c r="AM115" s="36"/>
+      <c r="AN115" s="36"/>
     </row>
     <row r="116" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A116" s="25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B116" s="26" t="s">
         <v>223</v>
@@ -9220,7 +9244,7 @@
         <v>224</v>
       </c>
       <c r="D116" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E116" s="25" t="s">
         <v>9</v>
@@ -9229,10 +9253,10 @@
         <v>0</v>
       </c>
       <c r="G116" s="28">
-        <v>46329</v>
+        <v>46325</v>
       </c>
       <c r="H116" s="28">
-        <v>46329</v>
+        <v>46325</v>
       </c>
       <c r="I116" s="29">
         <f>NETWORKDAYS(G116,H116)</f>
@@ -9273,7 +9297,7 @@
     </row>
     <row r="117" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A117" s="25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B117" s="26" t="s">
         <v>225</v>
@@ -9282,7 +9306,7 @@
         <v>226</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E117" s="25" t="s">
         <v>9</v>
@@ -9291,10 +9315,10 @@
         <v>0</v>
       </c>
       <c r="G117" s="28">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="H117" s="28">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="I117" s="29">
         <f>NETWORKDAYS(G117,H117)</f>
@@ -9335,7 +9359,7 @@
     </row>
     <row r="118" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A118" s="25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B118" s="26" t="s">
         <v>227</v>
@@ -9344,7 +9368,7 @@
         <v>228</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E118" s="25" t="s">
         <v>9</v>
@@ -9353,10 +9377,10 @@
         <v>0</v>
       </c>
       <c r="G118" s="28">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="H118" s="28">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="I118" s="29">
         <f>NETWORKDAYS(G118,H118)</f>
@@ -9397,7 +9421,7 @@
     </row>
     <row r="119" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A119" s="25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B119" s="26" t="s">
         <v>229</v>
@@ -9406,7 +9430,7 @@
         <v>230</v>
       </c>
       <c r="D119" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E119" s="25" t="s">
         <v>9</v>
@@ -9415,10 +9439,10 @@
         <v>0</v>
       </c>
       <c r="G119" s="28">
-        <v>46335</v>
+        <v>46329</v>
       </c>
       <c r="H119" s="28">
-        <v>46335</v>
+        <v>46329</v>
       </c>
       <c r="I119" s="29">
         <f>NETWORKDAYS(G119,H119)</f>
@@ -9459,16 +9483,16 @@
     </row>
     <row r="120" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A120" s="25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B120" s="26" t="s">
         <v>231</v>
       </c>
       <c r="C120" s="26" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D120" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E120" s="25" t="s">
         <v>9</v>
@@ -9477,10 +9501,10 @@
         <v>0</v>
       </c>
       <c r="G120" s="28">
-        <v>46335</v>
+        <v>46329</v>
       </c>
       <c r="H120" s="28">
-        <v>46335</v>
+        <v>46329</v>
       </c>
       <c r="I120" s="29">
         <f>NETWORKDAYS(G120,H120)</f>
@@ -9521,16 +9545,16 @@
     </row>
     <row r="121" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A121" s="25">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B121" s="26" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C121" s="26" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E121" s="25" t="s">
         <v>9</v>
@@ -9539,10 +9563,10 @@
         <v>0</v>
       </c>
       <c r="G121" s="28">
-        <v>46335</v>
+        <v>46330</v>
       </c>
       <c r="H121" s="28">
-        <v>46335</v>
+        <v>46330</v>
       </c>
       <c r="I121" s="29">
         <f>NETWORKDAYS(G121,H121)</f>
@@ -9583,16 +9607,16 @@
     </row>
     <row r="122" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A122" s="25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B122" s="26" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C122" s="26" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D122" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E122" s="25" t="s">
         <v>9</v>
@@ -9601,10 +9625,10 @@
         <v>0</v>
       </c>
       <c r="G122" s="28">
-        <v>46335</v>
+        <v>46330</v>
       </c>
       <c r="H122" s="28">
-        <v>46335</v>
+        <v>46330</v>
       </c>
       <c r="I122" s="29">
         <f>NETWORKDAYS(G122,H122)</f>
@@ -9645,17 +9669,17 @@
     </row>
     <row r="123" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A123" s="25">
+        <v>8</v>
+      </c>
+      <c r="B123" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="C123" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="D123" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B123" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="C123" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="D123" s="25" t="s">
-        <v>8</v>
-      </c>
       <c r="E123" s="25" t="s">
         <v>9</v>
       </c>
@@ -9663,10 +9687,10 @@
         <v>0</v>
       </c>
       <c r="G123" s="28">
-        <v>46336</v>
+        <v>46330</v>
       </c>
       <c r="H123" s="28">
-        <v>46336</v>
+        <v>46330</v>
       </c>
       <c r="I123" s="29">
         <f>NETWORKDAYS(G123,H123)</f>
@@ -9707,28 +9731,28 @@
     </row>
     <row r="124" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A124" s="25">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B124" s="26" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C124" s="26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D124" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E124" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E124" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="F124" s="27">
         <v>0</v>
       </c>
       <c r="G124" s="28">
-        <v>46336</v>
+        <v>46331</v>
       </c>
       <c r="H124" s="28">
-        <v>46336</v>
+        <v>46331</v>
       </c>
       <c r="I124" s="29">
         <f>NETWORKDAYS(G124,H124)</f>
@@ -9767,96 +9791,92 @@
       <c r="AM124" s="30"/>
       <c r="AN124" s="30"/>
     </row>
-    <row r="125" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A125" s="31">
-        <v>5</v>
-      </c>
-      <c r="B125" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="C125" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="D125" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="E125" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="F125" s="34">
-        <f>AVERAGE(F126:F142)</f>
-      </c>
-      <c r="G125" s="35">
-        <f>MIN(G126:G142)</f>
-      </c>
-      <c r="H125" s="35">
-        <f>MAX(H126:H142)</f>
-      </c>
-      <c r="I125" s="31">
+    <row r="125" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A125" s="25">
+        <v>10</v>
+      </c>
+      <c r="B125" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="C125" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="D125" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F125" s="27">
+        <v>0</v>
+      </c>
+      <c r="G125" s="28">
+        <v>46331</v>
+      </c>
+      <c r="H125" s="28">
+        <v>46331</v>
+      </c>
+      <c r="I125" s="29">
         <f>NETWORKDAYS(G125,H125)</f>
       </c>
-      <c r="J125" s="35">
-        <f>IF(COUNT(J126:J142)=0,"",MIN(J126:J142))</f>
-      </c>
-      <c r="K125" s="35">
-        <f>IF(COUNT(K126:K142)=0,"",MAX(K126:K142))</f>
-      </c>
-      <c r="L125" s="31">
+      <c r="J125" s="28"/>
+      <c r="K125" s="28"/>
+      <c r="L125" s="29">
         <f>IF(OR(J125="",K125=""),"",NETWORKDAYS(J125,K125))</f>
       </c>
-      <c r="M125" s="36"/>
-      <c r="N125" s="36"/>
-      <c r="O125" s="36"/>
-      <c r="P125" s="36"/>
-      <c r="Q125" s="36"/>
-      <c r="R125" s="36"/>
-      <c r="S125" s="36"/>
-      <c r="T125" s="36"/>
-      <c r="U125" s="36"/>
-      <c r="V125" s="36"/>
-      <c r="W125" s="36"/>
-      <c r="X125" s="36"/>
-      <c r="Y125" s="36"/>
-      <c r="Z125" s="36"/>
-      <c r="AA125" s="36"/>
-      <c r="AB125" s="36"/>
-      <c r="AC125" s="36"/>
-      <c r="AD125" s="36"/>
-      <c r="AE125" s="36"/>
-      <c r="AF125" s="36"/>
-      <c r="AG125" s="36"/>
-      <c r="AH125" s="36"/>
-      <c r="AI125" s="36"/>
-      <c r="AJ125" s="36"/>
-      <c r="AK125" s="36"/>
-      <c r="AL125" s="36"/>
-      <c r="AM125" s="36"/>
-      <c r="AN125" s="36"/>
+      <c r="M125" s="30"/>
+      <c r="N125" s="30"/>
+      <c r="O125" s="30"/>
+      <c r="P125" s="30"/>
+      <c r="Q125" s="30"/>
+      <c r="R125" s="30"/>
+      <c r="S125" s="30"/>
+      <c r="T125" s="30"/>
+      <c r="U125" s="30"/>
+      <c r="V125" s="30"/>
+      <c r="W125" s="30"/>
+      <c r="X125" s="30"/>
+      <c r="Y125" s="30"/>
+      <c r="Z125" s="30"/>
+      <c r="AA125" s="30"/>
+      <c r="AB125" s="30"/>
+      <c r="AC125" s="30"/>
+      <c r="AD125" s="30"/>
+      <c r="AE125" s="30"/>
+      <c r="AF125" s="30"/>
+      <c r="AG125" s="30"/>
+      <c r="AH125" s="30"/>
+      <c r="AI125" s="30"/>
+      <c r="AJ125" s="30"/>
+      <c r="AK125" s="30"/>
+      <c r="AL125" s="30"/>
+      <c r="AM125" s="30"/>
+      <c r="AN125" s="30"/>
     </row>
     <row r="126" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A126" s="25">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B126" s="26" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C126" s="26" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D126" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E126" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F126" s="27">
         <v>0</v>
       </c>
       <c r="G126" s="28">
-        <v>46328</v>
+        <v>46332</v>
       </c>
       <c r="H126" s="28">
-        <v>46328</v>
+        <v>46332</v>
       </c>
       <c r="I126" s="29">
         <f>NETWORKDAYS(G126,H126)</f>
@@ -9897,28 +9917,28 @@
     </row>
     <row r="127" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A127" s="25">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B127" s="26" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C127" s="26" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D127" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E127" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F127" s="27">
         <v>0</v>
       </c>
       <c r="G127" s="28">
-        <v>46328</v>
+        <v>46332</v>
       </c>
       <c r="H127" s="28">
-        <v>46328</v>
+        <v>46332</v>
       </c>
       <c r="I127" s="29">
         <f>NETWORKDAYS(G127,H127)</f>
@@ -9959,13 +9979,13 @@
     </row>
     <row r="128" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A128" s="25">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B128" s="26" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C128" s="26" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D128" s="25" t="s">
         <v>11</v>
@@ -9977,10 +9997,10 @@
         <v>0</v>
       </c>
       <c r="G128" s="28">
-        <v>46329</v>
+        <v>46332</v>
       </c>
       <c r="H128" s="28">
-        <v>46329</v>
+        <v>46332</v>
       </c>
       <c r="I128" s="29">
         <f>NETWORKDAYS(G128,H128)</f>
@@ -10021,28 +10041,28 @@
     </row>
     <row r="129" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A129" s="25">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B129" s="26" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C129" s="26" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D129" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E129" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F129" s="27">
         <v>0</v>
       </c>
       <c r="G129" s="28">
-        <v>46329</v>
+        <v>46335</v>
       </c>
       <c r="H129" s="28">
-        <v>46329</v>
+        <v>46335</v>
       </c>
       <c r="I129" s="29">
         <f>NETWORKDAYS(G129,H129)</f>
@@ -10083,28 +10103,28 @@
     </row>
     <row r="130" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A130" s="25">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B130" s="26" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C130" s="26" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D130" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E130" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F130" s="27">
         <v>0</v>
       </c>
       <c r="G130" s="28">
-        <v>46330</v>
+        <v>46335</v>
       </c>
       <c r="H130" s="28">
-        <v>46330</v>
+        <v>46335</v>
       </c>
       <c r="I130" s="29">
         <f>NETWORKDAYS(G130,H130)</f>
@@ -10145,28 +10165,28 @@
     </row>
     <row r="131" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A131" s="25">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B131" s="26" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C131" s="26" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D131" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E131" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F131" s="27">
         <v>0</v>
       </c>
       <c r="G131" s="28">
-        <v>46330</v>
+        <v>46336</v>
       </c>
       <c r="H131" s="28">
-        <v>46330</v>
+        <v>46336</v>
       </c>
       <c r="I131" s="29">
         <f>NETWORKDAYS(G131,H131)</f>
@@ -10207,28 +10227,28 @@
     </row>
     <row r="132" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A132" s="25">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B132" s="26" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C132" s="26" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D132" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E132" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F132" s="27">
         <v>0</v>
       </c>
       <c r="G132" s="28">
-        <v>46330</v>
+        <v>46336</v>
       </c>
       <c r="H132" s="28">
-        <v>46330</v>
+        <v>46336</v>
       </c>
       <c r="I132" s="29">
         <f>NETWORKDAYS(G132,H132)</f>
@@ -10267,80 +10287,84 @@
       <c r="AM132" s="30"/>
       <c r="AN132" s="30"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A133" s="25">
-        <v>8</v>
-      </c>
-      <c r="B133" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="C133" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="D133" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E133" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F133" s="27">
-        <v>0</v>
-      </c>
-      <c r="G133" s="28">
-        <v>46331</v>
-      </c>
-      <c r="H133" s="28">
-        <v>46331</v>
-      </c>
-      <c r="I133" s="29">
+    <row r="133" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A133" s="31">
+        <v>5</v>
+      </c>
+      <c r="B133" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="C133" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="D133" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E133" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F133" s="34">
+        <f>AVERAGE(F134:F145)</f>
+      </c>
+      <c r="G133" s="35">
+        <f>MIN(G134:G145)</f>
+      </c>
+      <c r="H133" s="35">
+        <f>MAX(H134:H145)</f>
+      </c>
+      <c r="I133" s="31">
         <f>NETWORKDAYS(G133,H133)</f>
       </c>
-      <c r="J133" s="28"/>
-      <c r="K133" s="28"/>
-      <c r="L133" s="29">
+      <c r="J133" s="35">
+        <f>IF(COUNT(J134:J145)=0,"",MIN(J134:J145))</f>
+      </c>
+      <c r="K133" s="35">
+        <f>IF(COUNT(K134:K145)=0,"",MAX(K134:K145))</f>
+      </c>
+      <c r="L133" s="31">
         <f>IF(OR(J133="",K133=""),"",NETWORKDAYS(J133,K133))</f>
       </c>
-      <c r="M133" s="30"/>
-      <c r="N133" s="30"/>
-      <c r="O133" s="30"/>
-      <c r="P133" s="30"/>
-      <c r="Q133" s="30"/>
-      <c r="R133" s="30"/>
-      <c r="S133" s="30"/>
-      <c r="T133" s="30"/>
-      <c r="U133" s="30"/>
-      <c r="V133" s="30"/>
-      <c r="W133" s="30"/>
-      <c r="X133" s="30"/>
-      <c r="Y133" s="30"/>
-      <c r="Z133" s="30"/>
-      <c r="AA133" s="30"/>
-      <c r="AB133" s="30"/>
-      <c r="AC133" s="30"/>
-      <c r="AD133" s="30"/>
-      <c r="AE133" s="30"/>
-      <c r="AF133" s="30"/>
-      <c r="AG133" s="30"/>
-      <c r="AH133" s="30"/>
-      <c r="AI133" s="30"/>
-      <c r="AJ133" s="30"/>
-      <c r="AK133" s="30"/>
-      <c r="AL133" s="30"/>
-      <c r="AM133" s="30"/>
-      <c r="AN133" s="30"/>
+      <c r="M133" s="36"/>
+      <c r="N133" s="36"/>
+      <c r="O133" s="36"/>
+      <c r="P133" s="36"/>
+      <c r="Q133" s="36"/>
+      <c r="R133" s="36"/>
+      <c r="S133" s="36"/>
+      <c r="T133" s="36"/>
+      <c r="U133" s="36"/>
+      <c r="V133" s="36"/>
+      <c r="W133" s="36"/>
+      <c r="X133" s="36"/>
+      <c r="Y133" s="36"/>
+      <c r="Z133" s="36"/>
+      <c r="AA133" s="36"/>
+      <c r="AB133" s="36"/>
+      <c r="AC133" s="36"/>
+      <c r="AD133" s="36"/>
+      <c r="AE133" s="36"/>
+      <c r="AF133" s="36"/>
+      <c r="AG133" s="36"/>
+      <c r="AH133" s="36"/>
+      <c r="AI133" s="36"/>
+      <c r="AJ133" s="36"/>
+      <c r="AK133" s="36"/>
+      <c r="AL133" s="36"/>
+      <c r="AM133" s="36"/>
+      <c r="AN133" s="36"/>
     </row>
     <row r="134" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A134" s="25">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B134" s="26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C134" s="26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D134" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E134" s="25" t="s">
         <v>9</v>
@@ -10349,10 +10373,10 @@
         <v>0</v>
       </c>
       <c r="G134" s="28">
-        <v>46331</v>
+        <v>46328</v>
       </c>
       <c r="H134" s="28">
-        <v>46331</v>
+        <v>46328</v>
       </c>
       <c r="I134" s="29">
         <f>NETWORKDAYS(G134,H134)</f>
@@ -10393,16 +10417,16 @@
     </row>
     <row r="135" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A135" s="25">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B135" s="26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C135" s="26" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D135" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E135" s="25" t="s">
         <v>9</v>
@@ -10411,10 +10435,10 @@
         <v>0</v>
       </c>
       <c r="G135" s="28">
-        <v>46331</v>
+        <v>46328</v>
       </c>
       <c r="H135" s="28">
-        <v>46331</v>
+        <v>46328</v>
       </c>
       <c r="I135" s="29">
         <f>NETWORKDAYS(G135,H135)</f>
@@ -10455,28 +10479,28 @@
     </row>
     <row r="136" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A136" s="25">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B136" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C136" s="26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D136" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E136" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F136" s="27">
         <v>0</v>
       </c>
       <c r="G136" s="28">
-        <v>46332</v>
+        <v>46328</v>
       </c>
       <c r="H136" s="28">
-        <v>46332</v>
+        <v>46328</v>
       </c>
       <c r="I136" s="29">
         <f>NETWORKDAYS(G136,H136)</f>
@@ -10517,28 +10541,28 @@
     </row>
     <row r="137" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A137" s="25">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B137" s="26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C137" s="26" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D137" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E137" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F137" s="27">
         <v>0</v>
       </c>
       <c r="G137" s="28">
-        <v>46332</v>
+        <v>46329</v>
       </c>
       <c r="H137" s="28">
-        <v>46332</v>
+        <v>46329</v>
       </c>
       <c r="I137" s="29">
         <f>NETWORKDAYS(G137,H137)</f>
@@ -10579,16 +10603,16 @@
     </row>
     <row r="138" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A138" s="25">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B138" s="26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C138" s="26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D138" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E138" s="25" t="s">
         <v>9</v>
@@ -10597,10 +10621,10 @@
         <v>0</v>
       </c>
       <c r="G138" s="28">
-        <v>46332</v>
+        <v>46329</v>
       </c>
       <c r="H138" s="28">
-        <v>46332</v>
+        <v>46329</v>
       </c>
       <c r="I138" s="29">
         <f>NETWORKDAYS(G138,H138)</f>
@@ -10641,28 +10665,28 @@
     </row>
     <row r="139" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A139" s="25">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B139" s="26" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C139" s="26" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D139" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F139" s="27">
         <v>0</v>
       </c>
       <c r="G139" s="28">
-        <v>46335</v>
+        <v>46329</v>
       </c>
       <c r="H139" s="28">
-        <v>46335</v>
+        <v>46329</v>
       </c>
       <c r="I139" s="29">
         <f>NETWORKDAYS(G139,H139)</f>
@@ -10703,19 +10727,19 @@
     </row>
     <row r="140" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A140" s="25">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B140" s="26" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C140" s="26" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E140" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F140" s="27">
         <v>0</v>
@@ -10765,28 +10789,28 @@
     </row>
     <row r="141" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A141" s="25">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B141" s="26" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C141" s="26" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D141" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F141" s="27">
         <v>0</v>
       </c>
       <c r="G141" s="28">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="H141" s="28">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="I141" s="29">
         <f>NETWORKDAYS(G141,H141)</f>
@@ -10827,28 +10851,28 @@
     </row>
     <row r="142" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A142" s="25">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B142" s="26" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C142" s="26" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D142" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E142" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F142" s="27">
         <v>0</v>
       </c>
       <c r="G142" s="28">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="H142" s="28">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="I142" s="29">
         <f>NETWORKDAYS(G142,H142)</f>
@@ -10887,96 +10911,92 @@
       <c r="AM142" s="30"/>
       <c r="AN142" s="30"/>
     </row>
-    <row r="143" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A143" s="31">
-        <v>6</v>
-      </c>
-      <c r="B143" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="C143" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="D143" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="E143" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="F143" s="34">
-        <f>AVERAGE(F144:F161)</f>
-      </c>
-      <c r="G143" s="35">
-        <f>MIN(G144:G161)</f>
-      </c>
-      <c r="H143" s="35">
-        <f>MAX(H144:H161)</f>
-      </c>
-      <c r="I143" s="31">
+    <row r="143" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A143" s="25">
+        <v>10</v>
+      </c>
+      <c r="B143" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="C143" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="D143" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F143" s="27">
+        <v>0</v>
+      </c>
+      <c r="G143" s="28">
+        <v>46336</v>
+      </c>
+      <c r="H143" s="28">
+        <v>46336</v>
+      </c>
+      <c r="I143" s="29">
         <f>NETWORKDAYS(G143,H143)</f>
       </c>
-      <c r="J143" s="35">
-        <f>IF(COUNT(J144:J161)=0,"",MIN(J144:J161))</f>
-      </c>
-      <c r="K143" s="35">
-        <f>IF(COUNT(K144:K161)=0,"",MAX(K144:K161))</f>
-      </c>
-      <c r="L143" s="31">
+      <c r="J143" s="28"/>
+      <c r="K143" s="28"/>
+      <c r="L143" s="29">
         <f>IF(OR(J143="",K143=""),"",NETWORKDAYS(J143,K143))</f>
       </c>
-      <c r="M143" s="36"/>
-      <c r="N143" s="36"/>
-      <c r="O143" s="36"/>
-      <c r="P143" s="36"/>
-      <c r="Q143" s="36"/>
-      <c r="R143" s="36"/>
-      <c r="S143" s="36"/>
-      <c r="T143" s="36"/>
-      <c r="U143" s="36"/>
-      <c r="V143" s="36"/>
-      <c r="W143" s="36"/>
-      <c r="X143" s="36"/>
-      <c r="Y143" s="36"/>
-      <c r="Z143" s="36"/>
-      <c r="AA143" s="36"/>
-      <c r="AB143" s="36"/>
-      <c r="AC143" s="36"/>
-      <c r="AD143" s="36"/>
-      <c r="AE143" s="36"/>
-      <c r="AF143" s="36"/>
-      <c r="AG143" s="36"/>
-      <c r="AH143" s="36"/>
-      <c r="AI143" s="36"/>
-      <c r="AJ143" s="36"/>
-      <c r="AK143" s="36"/>
-      <c r="AL143" s="36"/>
-      <c r="AM143" s="36"/>
-      <c r="AN143" s="36"/>
+      <c r="M143" s="30"/>
+      <c r="N143" s="30"/>
+      <c r="O143" s="30"/>
+      <c r="P143" s="30"/>
+      <c r="Q143" s="30"/>
+      <c r="R143" s="30"/>
+      <c r="S143" s="30"/>
+      <c r="T143" s="30"/>
+      <c r="U143" s="30"/>
+      <c r="V143" s="30"/>
+      <c r="W143" s="30"/>
+      <c r="X143" s="30"/>
+      <c r="Y143" s="30"/>
+      <c r="Z143" s="30"/>
+      <c r="AA143" s="30"/>
+      <c r="AB143" s="30"/>
+      <c r="AC143" s="30"/>
+      <c r="AD143" s="30"/>
+      <c r="AE143" s="30"/>
+      <c r="AF143" s="30"/>
+      <c r="AG143" s="30"/>
+      <c r="AH143" s="30"/>
+      <c r="AI143" s="30"/>
+      <c r="AJ143" s="30"/>
+      <c r="AK143" s="30"/>
+      <c r="AL143" s="30"/>
+      <c r="AM143" s="30"/>
+      <c r="AN143" s="30"/>
     </row>
     <row r="144" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A144" s="25">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B144" s="26" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C144" s="26" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D144" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E144" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F144" s="27">
         <v>0</v>
       </c>
       <c r="G144" s="28">
-        <v>46329</v>
+        <v>46336</v>
       </c>
       <c r="H144" s="28">
-        <v>46329</v>
+        <v>46336</v>
       </c>
       <c r="I144" s="29">
         <f>NETWORKDAYS(G144,H144)</f>
@@ -11017,28 +11037,28 @@
     </row>
     <row r="145" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A145" s="25">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B145" s="26" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C145" s="26" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D145" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E145" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F145" s="27">
         <v>0</v>
       </c>
       <c r="G145" s="28">
-        <v>46329</v>
+        <v>46336</v>
       </c>
       <c r="H145" s="28">
-        <v>46329</v>
+        <v>46336</v>
       </c>
       <c r="I145" s="29">
         <f>NETWORKDAYS(G145,H145)</f>
@@ -11077,71 +11097,75 @@
       <c r="AM145" s="30"/>
       <c r="AN145" s="30"/>
     </row>
-    <row r="146" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A146" s="25">
-        <v>3</v>
-      </c>
-      <c r="B146" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="C146" s="26" t="s">
+    <row r="146" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A146" s="31">
+        <v>6</v>
+      </c>
+      <c r="B146" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="D146" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E146" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F146" s="27">
-        <v>0</v>
-      </c>
-      <c r="G146" s="28">
-        <v>46329</v>
-      </c>
-      <c r="H146" s="28">
-        <v>46329</v>
-      </c>
-      <c r="I146" s="29">
+      <c r="C146" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="D146" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E146" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F146" s="34">
+        <f>AVERAGE(F147:F164)</f>
+      </c>
+      <c r="G146" s="35">
+        <f>MIN(G147:G164)</f>
+      </c>
+      <c r="H146" s="35">
+        <f>MAX(H147:H164)</f>
+      </c>
+      <c r="I146" s="31">
         <f>NETWORKDAYS(G146,H146)</f>
       </c>
-      <c r="J146" s="28"/>
-      <c r="K146" s="28"/>
-      <c r="L146" s="29">
+      <c r="J146" s="35">
+        <f>IF(COUNT(J147:J164)=0,"",MIN(J147:J164))</f>
+      </c>
+      <c r="K146" s="35">
+        <f>IF(COUNT(K147:K164)=0,"",MAX(K147:K164))</f>
+      </c>
+      <c r="L146" s="31">
         <f>IF(OR(J146="",K146=""),"",NETWORKDAYS(J146,K146))</f>
       </c>
-      <c r="M146" s="30"/>
-      <c r="N146" s="30"/>
-      <c r="O146" s="30"/>
-      <c r="P146" s="30"/>
-      <c r="Q146" s="30"/>
-      <c r="R146" s="30"/>
-      <c r="S146" s="30"/>
-      <c r="T146" s="30"/>
-      <c r="U146" s="30"/>
-      <c r="V146" s="30"/>
-      <c r="W146" s="30"/>
-      <c r="X146" s="30"/>
-      <c r="Y146" s="30"/>
-      <c r="Z146" s="30"/>
-      <c r="AA146" s="30"/>
-      <c r="AB146" s="30"/>
-      <c r="AC146" s="30"/>
-      <c r="AD146" s="30"/>
-      <c r="AE146" s="30"/>
-      <c r="AF146" s="30"/>
-      <c r="AG146" s="30"/>
-      <c r="AH146" s="30"/>
-      <c r="AI146" s="30"/>
-      <c r="AJ146" s="30"/>
-      <c r="AK146" s="30"/>
-      <c r="AL146" s="30"/>
-      <c r="AM146" s="30"/>
-      <c r="AN146" s="30"/>
+      <c r="M146" s="36"/>
+      <c r="N146" s="36"/>
+      <c r="O146" s="36"/>
+      <c r="P146" s="36"/>
+      <c r="Q146" s="36"/>
+      <c r="R146" s="36"/>
+      <c r="S146" s="36"/>
+      <c r="T146" s="36"/>
+      <c r="U146" s="36"/>
+      <c r="V146" s="36"/>
+      <c r="W146" s="36"/>
+      <c r="X146" s="36"/>
+      <c r="Y146" s="36"/>
+      <c r="Z146" s="36"/>
+      <c r="AA146" s="36"/>
+      <c r="AB146" s="36"/>
+      <c r="AC146" s="36"/>
+      <c r="AD146" s="36"/>
+      <c r="AE146" s="36"/>
+      <c r="AF146" s="36"/>
+      <c r="AG146" s="36"/>
+      <c r="AH146" s="36"/>
+      <c r="AI146" s="36"/>
+      <c r="AJ146" s="36"/>
+      <c r="AK146" s="36"/>
+      <c r="AL146" s="36"/>
+      <c r="AM146" s="36"/>
+      <c r="AN146" s="36"/>
     </row>
     <row r="147" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A147" s="25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B147" s="26" t="s">
         <v>282</v>
@@ -11203,7 +11227,7 @@
     </row>
     <row r="148" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A148" s="25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B148" s="26" t="s">
         <v>284</v>
@@ -11212,10 +11236,10 @@
         <v>285</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E148" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F148" s="27">
         <v>0</v>
@@ -11265,7 +11289,7 @@
     </row>
     <row r="149" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A149" s="25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B149" s="26" t="s">
         <v>286</v>
@@ -11274,10 +11298,10 @@
         <v>287</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E149" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F149" s="27">
         <v>0</v>
@@ -11327,7 +11351,7 @@
     </row>
     <row r="150" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A150" s="25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B150" s="26" t="s">
         <v>288</v>
@@ -11345,10 +11369,10 @@
         <v>0</v>
       </c>
       <c r="G150" s="28">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="H150" s="28">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="I150" s="29">
         <f>NETWORKDAYS(G150,H150)</f>
@@ -11389,7 +11413,7 @@
     </row>
     <row r="151" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A151" s="25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B151" s="26" t="s">
         <v>290</v>
@@ -11398,19 +11422,19 @@
         <v>291</v>
       </c>
       <c r="D151" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E151" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F151" s="27">
         <v>0</v>
       </c>
       <c r="G151" s="28">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="H151" s="28">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="I151" s="29">
         <f>NETWORKDAYS(G151,H151)</f>
@@ -11451,28 +11475,28 @@
     </row>
     <row r="152" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A152" s="25">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B152" s="26" t="s">
         <v>292</v>
       </c>
       <c r="C152" s="26" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="D152" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E152" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F152" s="27">
         <v>0</v>
       </c>
       <c r="G152" s="28">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="H152" s="28">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="I152" s="29">
         <f>NETWORKDAYS(G152,H152)</f>
@@ -11513,19 +11537,19 @@
     </row>
     <row r="153" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A153" s="25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B153" s="26" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C153" s="26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D153" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E153" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F153" s="27">
         <v>0</v>
@@ -11575,19 +11599,19 @@
     </row>
     <row r="154" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A154" s="25">
+        <v>8</v>
+      </c>
+      <c r="B154" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="C154" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="D154" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="25" t="s">
         <v>11</v>
-      </c>
-      <c r="B154" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="C154" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="D154" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E154" s="25" t="s">
-        <v>8</v>
       </c>
       <c r="F154" s="27">
         <v>0</v>
@@ -11637,19 +11661,19 @@
     </row>
     <row r="155" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A155" s="25">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B155" s="26" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C155" s="26" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D155" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E155" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F155" s="27">
         <v>0</v>
@@ -11699,7 +11723,7 @@
     </row>
     <row r="156" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A156" s="25">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B156" s="26" t="s">
         <v>299</v>
@@ -11708,19 +11732,19 @@
         <v>300</v>
       </c>
       <c r="D156" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E156" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F156" s="27">
         <v>0</v>
       </c>
       <c r="G156" s="28">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="H156" s="28">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="I156" s="29">
         <f>NETWORKDAYS(G156,H156)</f>
@@ -11761,7 +11785,7 @@
     </row>
     <row r="157" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A157" s="25">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B157" s="26" t="s">
         <v>301</v>
@@ -11770,19 +11794,19 @@
         <v>302</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E157" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F157" s="27">
         <v>0</v>
       </c>
       <c r="G157" s="28">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="H157" s="28">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="I157" s="29">
         <f>NETWORKDAYS(G157,H157)</f>
@@ -11823,28 +11847,28 @@
     </row>
     <row r="158" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A158" s="25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B158" s="26" t="s">
         <v>303</v>
       </c>
       <c r="C158" s="26" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E158" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F158" s="27">
         <v>0</v>
       </c>
       <c r="G158" s="28">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="H158" s="28">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="I158" s="29">
         <f>NETWORKDAYS(G158,H158)</f>
@@ -11885,19 +11909,19 @@
     </row>
     <row r="159" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A159" s="25">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B159" s="26" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C159" s="26" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D159" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E159" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F159" s="27">
         <v>0</v>
@@ -11947,13 +11971,13 @@
     </row>
     <row r="160" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A160" s="25">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B160" s="26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C160" s="26" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="D160" s="25" t="s">
         <v>9</v>
@@ -11965,10 +11989,10 @@
         <v>0</v>
       </c>
       <c r="G160" s="28">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="H160" s="28">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="I160" s="29">
         <f>NETWORKDAYS(G160,H160)</f>
@@ -12009,13 +12033,13 @@
     </row>
     <row r="161" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A161" s="25">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B161" s="26" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C161" s="26" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="D161" s="25" t="s">
         <v>9</v>
@@ -12027,10 +12051,10 @@
         <v>0</v>
       </c>
       <c r="G161" s="28">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="H161" s="28">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="I161" s="29">
         <f>NETWORKDAYS(G161,H161)</f>
@@ -12069,96 +12093,92 @@
       <c r="AM161" s="30"/>
       <c r="AN161" s="30"/>
     </row>
-    <row r="162" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A162" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="B162" s="20" t="s">
+    <row r="162" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A162" s="25">
+        <v>16</v>
+      </c>
+      <c r="B162" s="26" t="s">
         <v>310</v>
       </c>
-      <c r="C162" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D162" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E162" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F162" s="22">
-        <f>AVERAGE(F163:F197)</f>
-      </c>
-      <c r="G162" s="23">
-        <f>MIN(G163:G197)</f>
-      </c>
-      <c r="H162" s="23">
-        <f>MAX(H163:H197)</f>
-      </c>
-      <c r="I162" s="19">
+      <c r="C162" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D162" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E162" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F162" s="27">
+        <v>0</v>
+      </c>
+      <c r="G162" s="28">
+        <v>46331</v>
+      </c>
+      <c r="H162" s="28">
+        <v>46331</v>
+      </c>
+      <c r="I162" s="29">
         <f>NETWORKDAYS(G162,H162)</f>
       </c>
-      <c r="J162" s="23">
-        <f>IF(COUNT(J163:J197)=0,"",MIN(J163:J197))</f>
-      </c>
-      <c r="K162" s="23">
-        <f>IF(COUNT(K163:K197)=0,"",MAX(K163:K197))</f>
-      </c>
-      <c r="L162" s="19">
+      <c r="J162" s="28"/>
+      <c r="K162" s="28"/>
+      <c r="L162" s="29">
         <f>IF(OR(J162="",K162=""),"",NETWORKDAYS(J162,K162))</f>
       </c>
-      <c r="M162" s="24"/>
-      <c r="N162" s="24"/>
-      <c r="O162" s="24"/>
-      <c r="P162" s="24"/>
-      <c r="Q162" s="24"/>
-      <c r="R162" s="24"/>
-      <c r="S162" s="24"/>
-      <c r="T162" s="24"/>
-      <c r="U162" s="24"/>
-      <c r="V162" s="24"/>
-      <c r="W162" s="24"/>
-      <c r="X162" s="24"/>
-      <c r="Y162" s="24"/>
-      <c r="Z162" s="24"/>
-      <c r="AA162" s="24"/>
-      <c r="AB162" s="24"/>
-      <c r="AC162" s="24"/>
-      <c r="AD162" s="24"/>
-      <c r="AE162" s="24"/>
-      <c r="AF162" s="24"/>
-      <c r="AG162" s="24"/>
-      <c r="AH162" s="24"/>
-      <c r="AI162" s="24"/>
-      <c r="AJ162" s="24"/>
-      <c r="AK162" s="24"/>
-      <c r="AL162" s="24"/>
-      <c r="AM162" s="24"/>
-      <c r="AN162" s="24"/>
+      <c r="M162" s="30"/>
+      <c r="N162" s="30"/>
+      <c r="O162" s="30"/>
+      <c r="P162" s="30"/>
+      <c r="Q162" s="30"/>
+      <c r="R162" s="30"/>
+      <c r="S162" s="30"/>
+      <c r="T162" s="30"/>
+      <c r="U162" s="30"/>
+      <c r="V162" s="30"/>
+      <c r="W162" s="30"/>
+      <c r="X162" s="30"/>
+      <c r="Y162" s="30"/>
+      <c r="Z162" s="30"/>
+      <c r="AA162" s="30"/>
+      <c r="AB162" s="30"/>
+      <c r="AC162" s="30"/>
+      <c r="AD162" s="30"/>
+      <c r="AE162" s="30"/>
+      <c r="AF162" s="30"/>
+      <c r="AG162" s="30"/>
+      <c r="AH162" s="30"/>
+      <c r="AI162" s="30"/>
+      <c r="AJ162" s="30"/>
+      <c r="AK162" s="30"/>
+      <c r="AL162" s="30"/>
+      <c r="AM162" s="30"/>
+      <c r="AN162" s="30"/>
     </row>
     <row r="163" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A163" s="25">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B163" s="26" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C163" s="26" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="D163" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E163" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F163" s="27">
         <v>0</v>
       </c>
       <c r="G163" s="28">
-        <v>46323</v>
+        <v>46332</v>
       </c>
       <c r="H163" s="28">
-        <v>46323</v>
+        <v>46332</v>
       </c>
       <c r="I163" s="29">
         <f>NETWORKDAYS(G163,H163)</f>
@@ -12199,7 +12219,7 @@
     </row>
     <row r="164" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A164" s="25">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B164" s="26" t="s">
         <v>313</v>
@@ -12208,19 +12228,19 @@
         <v>314</v>
       </c>
       <c r="D164" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E164" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F164" s="27">
         <v>0</v>
       </c>
       <c r="G164" s="28">
-        <v>46324</v>
+        <v>46332</v>
       </c>
       <c r="H164" s="28">
-        <v>46324</v>
+        <v>46332</v>
       </c>
       <c r="I164" s="29">
         <f>NETWORKDAYS(G164,H164)</f>
@@ -12259,71 +12279,75 @@
       <c r="AM164" s="30"/>
       <c r="AN164" s="30"/>
     </row>
-    <row r="165" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A165" s="25">
-        <v>3</v>
-      </c>
-      <c r="B165" s="26" t="s">
+    <row r="165" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A165" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="C165" s="26" t="s">
+      <c r="B165" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="D165" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E165" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F165" s="27">
-        <v>0</v>
-      </c>
-      <c r="G165" s="28">
-        <v>46324</v>
-      </c>
-      <c r="H165" s="28">
-        <v>46324</v>
-      </c>
-      <c r="I165" s="29">
+      <c r="C165" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D165" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E165" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F165" s="22">
+        <f>AVERAGE(F166:F200)</f>
+      </c>
+      <c r="G165" s="23">
+        <f>MIN(G166:G200)</f>
+      </c>
+      <c r="H165" s="23">
+        <f>MAX(H166:H200)</f>
+      </c>
+      <c r="I165" s="19">
         <f>NETWORKDAYS(G165,H165)</f>
       </c>
-      <c r="J165" s="28"/>
-      <c r="K165" s="28"/>
-      <c r="L165" s="29">
+      <c r="J165" s="23">
+        <f>IF(COUNT(J166:J200)=0,"",MIN(J166:J200))</f>
+      </c>
+      <c r="K165" s="23">
+        <f>IF(COUNT(K166:K200)=0,"",MAX(K166:K200))</f>
+      </c>
+      <c r="L165" s="19">
         <f>IF(OR(J165="",K165=""),"",NETWORKDAYS(J165,K165))</f>
       </c>
-      <c r="M165" s="30"/>
-      <c r="N165" s="30"/>
-      <c r="O165" s="30"/>
-      <c r="P165" s="30"/>
-      <c r="Q165" s="30"/>
-      <c r="R165" s="30"/>
-      <c r="S165" s="30"/>
-      <c r="T165" s="30"/>
-      <c r="U165" s="30"/>
-      <c r="V165" s="30"/>
-      <c r="W165" s="30"/>
-      <c r="X165" s="30"/>
-      <c r="Y165" s="30"/>
-      <c r="Z165" s="30"/>
-      <c r="AA165" s="30"/>
-      <c r="AB165" s="30"/>
-      <c r="AC165" s="30"/>
-      <c r="AD165" s="30"/>
-      <c r="AE165" s="30"/>
-      <c r="AF165" s="30"/>
-      <c r="AG165" s="30"/>
-      <c r="AH165" s="30"/>
-      <c r="AI165" s="30"/>
-      <c r="AJ165" s="30"/>
-      <c r="AK165" s="30"/>
-      <c r="AL165" s="30"/>
-      <c r="AM165" s="30"/>
-      <c r="AN165" s="30"/>
+      <c r="M165" s="24"/>
+      <c r="N165" s="24"/>
+      <c r="O165" s="24"/>
+      <c r="P165" s="24"/>
+      <c r="Q165" s="24"/>
+      <c r="R165" s="24"/>
+      <c r="S165" s="24"/>
+      <c r="T165" s="24"/>
+      <c r="U165" s="24"/>
+      <c r="V165" s="24"/>
+      <c r="W165" s="24"/>
+      <c r="X165" s="24"/>
+      <c r="Y165" s="24"/>
+      <c r="Z165" s="24"/>
+      <c r="AA165" s="24"/>
+      <c r="AB165" s="24"/>
+      <c r="AC165" s="24"/>
+      <c r="AD165" s="24"/>
+      <c r="AE165" s="24"/>
+      <c r="AF165" s="24"/>
+      <c r="AG165" s="24"/>
+      <c r="AH165" s="24"/>
+      <c r="AI165" s="24"/>
+      <c r="AJ165" s="24"/>
+      <c r="AK165" s="24"/>
+      <c r="AL165" s="24"/>
+      <c r="AM165" s="24"/>
+      <c r="AN165" s="24"/>
     </row>
     <row r="166" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A166" s="25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B166" s="26" t="s">
         <v>317</v>
@@ -12341,10 +12365,10 @@
         <v>0</v>
       </c>
       <c r="G166" s="28">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="H166" s="28">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="I166" s="29">
         <f>NETWORKDAYS(G166,H166)</f>
@@ -12385,7 +12409,7 @@
     </row>
     <row r="167" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A167" s="25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B167" s="26" t="s">
         <v>319</v>
@@ -12394,7 +12418,7 @@
         <v>320</v>
       </c>
       <c r="D167" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E167" s="25" t="s">
         <v>9</v>
@@ -12447,7 +12471,7 @@
     </row>
     <row r="168" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A168" s="25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B168" s="26" t="s">
         <v>321</v>
@@ -12465,10 +12489,10 @@
         <v>0</v>
       </c>
       <c r="G168" s="28">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="H168" s="28">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="I168" s="29">
         <f>NETWORKDAYS(G168,H168)</f>
@@ -12509,7 +12533,7 @@
     </row>
     <row r="169" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A169" s="25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B169" s="26" t="s">
         <v>323</v>
@@ -12527,10 +12551,10 @@
         <v>0</v>
       </c>
       <c r="G169" s="28">
-        <v>46330</v>
+        <v>46324</v>
       </c>
       <c r="H169" s="28">
-        <v>46330</v>
+        <v>46324</v>
       </c>
       <c r="I169" s="29">
         <f>NETWORKDAYS(G169,H169)</f>
@@ -12571,7 +12595,7 @@
     </row>
     <row r="170" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A170" s="25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B170" s="26" t="s">
         <v>325</v>
@@ -12580,7 +12604,7 @@
         <v>326</v>
       </c>
       <c r="D170" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E170" s="25" t="s">
         <v>9</v>
@@ -12589,10 +12613,10 @@
         <v>0</v>
       </c>
       <c r="G170" s="28">
-        <v>46330</v>
+        <v>46324</v>
       </c>
       <c r="H170" s="28">
-        <v>46330</v>
+        <v>46324</v>
       </c>
       <c r="I170" s="29">
         <f>NETWORKDAYS(G170,H170)</f>
@@ -12633,7 +12657,7 @@
     </row>
     <row r="171" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A171" s="25">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B171" s="26" t="s">
         <v>327</v>
@@ -12651,10 +12675,10 @@
         <v>0</v>
       </c>
       <c r="G171" s="28">
-        <v>46331</v>
+        <v>46325</v>
       </c>
       <c r="H171" s="28">
-        <v>46331</v>
+        <v>46325</v>
       </c>
       <c r="I171" s="29">
         <f>NETWORKDAYS(G171,H171)</f>
@@ -12695,7 +12719,7 @@
     </row>
     <row r="172" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A172" s="25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B172" s="26" t="s">
         <v>329</v>
@@ -12713,10 +12737,10 @@
         <v>0</v>
       </c>
       <c r="G172" s="28">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="H172" s="28">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="I172" s="29">
         <f>NETWORKDAYS(G172,H172)</f>
@@ -12757,7 +12781,7 @@
     </row>
     <row r="173" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A173" s="25">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B173" s="26" t="s">
         <v>331</v>
@@ -12775,10 +12799,10 @@
         <v>0</v>
       </c>
       <c r="G173" s="28">
-        <v>46332</v>
+        <v>46330</v>
       </c>
       <c r="H173" s="28">
-        <v>46332</v>
+        <v>46330</v>
       </c>
       <c r="I173" s="29">
         <f>NETWORKDAYS(G173,H173)</f>
@@ -12819,7 +12843,7 @@
     </row>
     <row r="174" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A174" s="25">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B174" s="26" t="s">
         <v>333</v>
@@ -12828,7 +12852,7 @@
         <v>334</v>
       </c>
       <c r="D174" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E174" s="25" t="s">
         <v>9</v>
@@ -12837,10 +12861,10 @@
         <v>0</v>
       </c>
       <c r="G174" s="28">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="H174" s="28">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="I174" s="29">
         <f>NETWORKDAYS(G174,H174)</f>
@@ -12881,7 +12905,7 @@
     </row>
     <row r="175" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A175" s="25">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B175" s="26" t="s">
         <v>335</v>
@@ -12890,19 +12914,19 @@
         <v>336</v>
       </c>
       <c r="D175" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E175" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F175" s="27">
         <v>0</v>
       </c>
       <c r="G175" s="28">
-        <v>46335</v>
+        <v>46331</v>
       </c>
       <c r="H175" s="28">
-        <v>46335</v>
+        <v>46331</v>
       </c>
       <c r="I175" s="29">
         <f>NETWORKDAYS(G175,H175)</f>
@@ -12943,7 +12967,7 @@
     </row>
     <row r="176" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A176" s="25">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B176" s="26" t="s">
         <v>337</v>
@@ -12952,19 +12976,19 @@
         <v>338</v>
       </c>
       <c r="D176" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E176" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F176" s="27">
         <v>0</v>
       </c>
       <c r="G176" s="28">
-        <v>46335</v>
+        <v>46332</v>
       </c>
       <c r="H176" s="28">
-        <v>46335</v>
+        <v>46332</v>
       </c>
       <c r="I176" s="29">
         <f>NETWORKDAYS(G176,H176)</f>
@@ -13005,7 +13029,7 @@
     </row>
     <row r="177" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A177" s="25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B177" s="26" t="s">
         <v>339</v>
@@ -13014,19 +13038,19 @@
         <v>340</v>
       </c>
       <c r="D177" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E177" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F177" s="27">
         <v>0</v>
       </c>
       <c r="G177" s="28">
-        <v>46335</v>
+        <v>46332</v>
       </c>
       <c r="H177" s="28">
-        <v>46335</v>
+        <v>46332</v>
       </c>
       <c r="I177" s="29">
         <f>NETWORKDAYS(G177,H177)</f>
@@ -13067,7 +13091,7 @@
     </row>
     <row r="178" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A178" s="25">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B178" s="26" t="s">
         <v>341</v>
@@ -13085,10 +13109,10 @@
         <v>0</v>
       </c>
       <c r="G178" s="28">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="H178" s="28">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="I178" s="29">
         <f>NETWORKDAYS(G178,H178)</f>
@@ -13129,13 +13153,13 @@
     </row>
     <row r="179" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A179" s="25">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B179" s="26" t="s">
         <v>343</v>
       </c>
       <c r="C179" s="26" t="s">
-        <v>254</v>
+        <v>344</v>
       </c>
       <c r="D179" s="25" t="s">
         <v>9</v>
@@ -13147,10 +13171,10 @@
         <v>0</v>
       </c>
       <c r="G179" s="28">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="H179" s="28">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="I179" s="29">
         <f>NETWORKDAYS(G179,H179)</f>
@@ -13191,28 +13215,28 @@
     </row>
     <row r="180" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A180" s="25">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B180" s="26" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C180" s="26" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D180" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E180" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F180" s="27">
         <v>0</v>
       </c>
       <c r="G180" s="28">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="H180" s="28">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="I180" s="29">
         <f>NETWORKDAYS(G180,H180)</f>
@@ -13253,28 +13277,28 @@
     </row>
     <row r="181" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A181" s="25">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B181" s="26" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C181" s="26" t="s">
-        <v>347</v>
+        <v>238</v>
       </c>
       <c r="D181" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E181" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F181" s="27">
         <v>0</v>
       </c>
       <c r="G181" s="28">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="H181" s="28">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="I181" s="29">
         <f>NETWORKDAYS(G181,H181)</f>
@@ -13315,7 +13339,7 @@
     </row>
     <row r="182" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A182" s="25">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B182" s="26" t="s">
         <v>348</v>
@@ -13377,7 +13401,7 @@
     </row>
     <row r="183" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A183" s="25">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B183" s="26" t="s">
         <v>350</v>
@@ -13386,10 +13410,10 @@
         <v>351</v>
       </c>
       <c r="D183" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E183" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F183" s="27">
         <v>0</v>
@@ -13439,19 +13463,19 @@
     </row>
     <row r="184" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A184" s="25">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B184" s="26" t="s">
         <v>352</v>
       </c>
       <c r="C184" s="26" t="s">
-        <v>308</v>
+        <v>353</v>
       </c>
       <c r="D184" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E184" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F184" s="27">
         <v>0</v>
@@ -13501,19 +13525,19 @@
     </row>
     <row r="185" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A185" s="25">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B185" s="26" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C185" s="26" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D185" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E185" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F185" s="27">
         <v>0</v>
@@ -13563,19 +13587,19 @@
     </row>
     <row r="186" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A186" s="25">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B186" s="26" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C186" s="26" t="s">
-        <v>356</v>
+        <v>314</v>
       </c>
       <c r="D186" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E186" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F186" s="27">
         <v>0</v>
@@ -13625,7 +13649,7 @@
     </row>
     <row r="187" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A187" s="25">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B187" s="26" t="s">
         <v>357</v>
@@ -13634,19 +13658,19 @@
         <v>358</v>
       </c>
       <c r="D187" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E187" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F187" s="27">
         <v>0</v>
       </c>
       <c r="G187" s="28">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="H187" s="28">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="I187" s="29">
         <f>NETWORKDAYS(G187,H187)</f>
@@ -13687,7 +13711,7 @@
     </row>
     <row r="188" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A188" s="25">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B188" s="26" t="s">
         <v>359</v>
@@ -13696,19 +13720,19 @@
         <v>360</v>
       </c>
       <c r="D188" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E188" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E188" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="F188" s="27">
         <v>0</v>
       </c>
       <c r="G188" s="28">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="H188" s="28">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="I188" s="29">
         <f>NETWORKDAYS(G188,H188)</f>
@@ -13749,7 +13773,7 @@
     </row>
     <row r="189" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A189" s="25">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B189" s="26" t="s">
         <v>361</v>
@@ -13758,19 +13782,19 @@
         <v>362</v>
       </c>
       <c r="D189" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E189" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F189" s="27">
         <v>0</v>
       </c>
       <c r="G189" s="28">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="H189" s="28">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="I189" s="29">
         <f>NETWORKDAYS(G189,H189)</f>
@@ -13811,7 +13835,7 @@
     </row>
     <row r="190" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A190" s="25">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B190" s="26" t="s">
         <v>363</v>
@@ -13820,10 +13844,10 @@
         <v>364</v>
       </c>
       <c r="D190" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E190" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F190" s="27">
         <v>0</v>
@@ -13873,7 +13897,7 @@
     </row>
     <row r="191" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A191" s="25">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B191" s="26" t="s">
         <v>365</v>
@@ -13882,10 +13906,10 @@
         <v>366</v>
       </c>
       <c r="D191" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E191" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F191" s="27">
         <v>0</v>
@@ -13935,19 +13959,19 @@
     </row>
     <row r="192" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A192" s="25">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B192" s="26" t="s">
         <v>367</v>
       </c>
       <c r="C192" s="26" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D192" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" s="25" t="s">
         <v>11</v>
-      </c>
-      <c r="E192" s="25" t="s">
-        <v>9</v>
       </c>
       <c r="F192" s="27">
         <v>0</v>
@@ -13997,28 +14021,28 @@
     </row>
     <row r="193" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A193" s="25">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B193" s="26" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C193" s="26" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D193" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E193" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E193" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="F193" s="27">
         <v>0</v>
       </c>
       <c r="G193" s="28">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="H193" s="28">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="I193" s="29">
         <f>NETWORKDAYS(G193,H193)</f>
@@ -14059,28 +14083,28 @@
     </row>
     <row r="194" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A194" s="25">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B194" s="26" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C194" s="26" t="s">
-        <v>308</v>
+        <v>372</v>
       </c>
       <c r="D194" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E194" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F194" s="27">
         <v>0</v>
       </c>
       <c r="G194" s="28">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="H194" s="28">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="I194" s="29">
         <f>NETWORKDAYS(G194,H194)</f>
@@ -14121,28 +14145,28 @@
     </row>
     <row r="195" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A195" s="25">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B195" s="26" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C195" s="26" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D195" s="25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E195" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F195" s="27">
         <v>0</v>
       </c>
       <c r="G195" s="28">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="H195" s="28">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="I195" s="29">
         <f>NETWORKDAYS(G195,H195)</f>
@@ -14183,19 +14207,19 @@
     </row>
     <row r="196" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A196" s="25">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B196" s="26" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C196" s="26" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D196" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E196" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F196" s="27">
         <v>0</v>
@@ -14245,19 +14269,19 @@
     </row>
     <row r="197" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A197" s="25">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B197" s="26" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C197" s="26" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="D197" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E197" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F197" s="27">
         <v>0</v>
@@ -14305,75 +14329,71 @@
       <c r="AM197" s="30"/>
       <c r="AN197" s="30"/>
     </row>
-    <row r="198" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A198" s="19" t="s">
+    <row r="198" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A198" s="25">
+        <v>33</v>
+      </c>
+      <c r="B198" s="26" t="s">
         <v>377</v>
       </c>
-      <c r="B198" s="20" t="s">
+      <c r="C198" s="26" t="s">
         <v>378</v>
       </c>
-      <c r="C198" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D198" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E198" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F198" s="22">
-        <f>AVERAGE(F199:F215)</f>
-      </c>
-      <c r="G198" s="23">
-        <f>MIN(G199:G215)</f>
-      </c>
-      <c r="H198" s="23">
-        <f>MAX(H199:H215)</f>
-      </c>
-      <c r="I198" s="19">
+      <c r="D198" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E198" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F198" s="27">
+        <v>0</v>
+      </c>
+      <c r="G198" s="28">
+        <v>46339</v>
+      </c>
+      <c r="H198" s="28">
+        <v>46339</v>
+      </c>
+      <c r="I198" s="29">
         <f>NETWORKDAYS(G198,H198)</f>
       </c>
-      <c r="J198" s="23">
-        <f>IF(COUNT(J199:J215)=0,"",MIN(J199:J215))</f>
-      </c>
-      <c r="K198" s="23">
-        <f>IF(COUNT(K199:K215)=0,"",MAX(K199:K215))</f>
-      </c>
-      <c r="L198" s="19">
+      <c r="J198" s="28"/>
+      <c r="K198" s="28"/>
+      <c r="L198" s="29">
         <f>IF(OR(J198="",K198=""),"",NETWORKDAYS(J198,K198))</f>
       </c>
-      <c r="M198" s="24"/>
-      <c r="N198" s="24"/>
-      <c r="O198" s="24"/>
-      <c r="P198" s="24"/>
-      <c r="Q198" s="24"/>
-      <c r="R198" s="24"/>
-      <c r="S198" s="24"/>
-      <c r="T198" s="24"/>
-      <c r="U198" s="24"/>
-      <c r="V198" s="24"/>
-      <c r="W198" s="24"/>
-      <c r="X198" s="24"/>
-      <c r="Y198" s="24"/>
-      <c r="Z198" s="24"/>
-      <c r="AA198" s="24"/>
-      <c r="AB198" s="24"/>
-      <c r="AC198" s="24"/>
-      <c r="AD198" s="24"/>
-      <c r="AE198" s="24"/>
-      <c r="AF198" s="24"/>
-      <c r="AG198" s="24"/>
-      <c r="AH198" s="24"/>
-      <c r="AI198" s="24"/>
-      <c r="AJ198" s="24"/>
-      <c r="AK198" s="24"/>
-      <c r="AL198" s="24"/>
-      <c r="AM198" s="24"/>
-      <c r="AN198" s="24"/>
+      <c r="M198" s="30"/>
+      <c r="N198" s="30"/>
+      <c r="O198" s="30"/>
+      <c r="P198" s="30"/>
+      <c r="Q198" s="30"/>
+      <c r="R198" s="30"/>
+      <c r="S198" s="30"/>
+      <c r="T198" s="30"/>
+      <c r="U198" s="30"/>
+      <c r="V198" s="30"/>
+      <c r="W198" s="30"/>
+      <c r="X198" s="30"/>
+      <c r="Y198" s="30"/>
+      <c r="Z198" s="30"/>
+      <c r="AA198" s="30"/>
+      <c r="AB198" s="30"/>
+      <c r="AC198" s="30"/>
+      <c r="AD198" s="30"/>
+      <c r="AE198" s="30"/>
+      <c r="AF198" s="30"/>
+      <c r="AG198" s="30"/>
+      <c r="AH198" s="30"/>
+      <c r="AI198" s="30"/>
+      <c r="AJ198" s="30"/>
+      <c r="AK198" s="30"/>
+      <c r="AL198" s="30"/>
+      <c r="AM198" s="30"/>
+      <c r="AN198" s="30"/>
     </row>
     <row r="199" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A199" s="25">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B199" s="26" t="s">
         <v>379</v>
@@ -14382,19 +14402,19 @@
         <v>380</v>
       </c>
       <c r="D199" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E199" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F199" s="27">
         <v>0</v>
       </c>
       <c r="G199" s="28">
-        <v>46325</v>
+        <v>46339</v>
       </c>
       <c r="H199" s="28">
-        <v>46325</v>
+        <v>46339</v>
       </c>
       <c r="I199" s="29">
         <f>NETWORKDAYS(G199,H199)</f>
@@ -14435,7 +14455,7 @@
     </row>
     <row r="200" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A200" s="25">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B200" s="26" t="s">
         <v>381</v>
@@ -14444,19 +14464,19 @@
         <v>382</v>
       </c>
       <c r="D200" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E200" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F200" s="27">
         <v>0</v>
       </c>
       <c r="G200" s="28">
-        <v>46331</v>
+        <v>46339</v>
       </c>
       <c r="H200" s="28">
-        <v>46331</v>
+        <v>46339</v>
       </c>
       <c r="I200" s="29">
         <f>NETWORKDAYS(G200,H200)</f>
@@ -14495,71 +14515,75 @@
       <c r="AM200" s="30"/>
       <c r="AN200" s="30"/>
     </row>
-    <row r="201" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A201" s="25">
-        <v>3</v>
-      </c>
-      <c r="B201" s="26" t="s">
+    <row r="201" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A201" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="C201" s="26" t="s">
+      <c r="B201" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="D201" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E201" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F201" s="27">
-        <v>0</v>
-      </c>
-      <c r="G201" s="28">
-        <v>46332</v>
-      </c>
-      <c r="H201" s="28">
-        <v>46332</v>
-      </c>
-      <c r="I201" s="29">
+      <c r="C201" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D201" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E201" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F201" s="22">
+        <f>AVERAGE(F202:F219)</f>
+      </c>
+      <c r="G201" s="23">
+        <f>MIN(G202:G219)</f>
+      </c>
+      <c r="H201" s="23">
+        <f>MAX(H202:H219)</f>
+      </c>
+      <c r="I201" s="19">
         <f>NETWORKDAYS(G201,H201)</f>
       </c>
-      <c r="J201" s="28"/>
-      <c r="K201" s="28"/>
-      <c r="L201" s="29">
+      <c r="J201" s="23">
+        <f>IF(COUNT(J202:J219)=0,"",MIN(J202:J219))</f>
+      </c>
+      <c r="K201" s="23">
+        <f>IF(COUNT(K202:K219)=0,"",MAX(K202:K219))</f>
+      </c>
+      <c r="L201" s="19">
         <f>IF(OR(J201="",K201=""),"",NETWORKDAYS(J201,K201))</f>
       </c>
-      <c r="M201" s="30"/>
-      <c r="N201" s="30"/>
-      <c r="O201" s="30"/>
-      <c r="P201" s="30"/>
-      <c r="Q201" s="30"/>
-      <c r="R201" s="30"/>
-      <c r="S201" s="30"/>
-      <c r="T201" s="30"/>
-      <c r="U201" s="30"/>
-      <c r="V201" s="30"/>
-      <c r="W201" s="30"/>
-      <c r="X201" s="30"/>
-      <c r="Y201" s="30"/>
-      <c r="Z201" s="30"/>
-      <c r="AA201" s="30"/>
-      <c r="AB201" s="30"/>
-      <c r="AC201" s="30"/>
-      <c r="AD201" s="30"/>
-      <c r="AE201" s="30"/>
-      <c r="AF201" s="30"/>
-      <c r="AG201" s="30"/>
-      <c r="AH201" s="30"/>
-      <c r="AI201" s="30"/>
-      <c r="AJ201" s="30"/>
-      <c r="AK201" s="30"/>
-      <c r="AL201" s="30"/>
-      <c r="AM201" s="30"/>
-      <c r="AN201" s="30"/>
+      <c r="M201" s="24"/>
+      <c r="N201" s="24"/>
+      <c r="O201" s="24"/>
+      <c r="P201" s="24"/>
+      <c r="Q201" s="24"/>
+      <c r="R201" s="24"/>
+      <c r="S201" s="24"/>
+      <c r="T201" s="24"/>
+      <c r="U201" s="24"/>
+      <c r="V201" s="24"/>
+      <c r="W201" s="24"/>
+      <c r="X201" s="24"/>
+      <c r="Y201" s="24"/>
+      <c r="Z201" s="24"/>
+      <c r="AA201" s="24"/>
+      <c r="AB201" s="24"/>
+      <c r="AC201" s="24"/>
+      <c r="AD201" s="24"/>
+      <c r="AE201" s="24"/>
+      <c r="AF201" s="24"/>
+      <c r="AG201" s="24"/>
+      <c r="AH201" s="24"/>
+      <c r="AI201" s="24"/>
+      <c r="AJ201" s="24"/>
+      <c r="AK201" s="24"/>
+      <c r="AL201" s="24"/>
+      <c r="AM201" s="24"/>
+      <c r="AN201" s="24"/>
     </row>
     <row r="202" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A202" s="25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B202" s="26" t="s">
         <v>385</v>
@@ -14577,10 +14601,10 @@
         <v>0</v>
       </c>
       <c r="G202" s="28">
-        <v>46335</v>
+        <v>46322</v>
       </c>
       <c r="H202" s="28">
-        <v>46335</v>
+        <v>46322</v>
       </c>
       <c r="I202" s="29">
         <f>NETWORKDAYS(G202,H202)</f>
@@ -14621,7 +14645,7 @@
     </row>
     <row r="203" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A203" s="25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B203" s="26" t="s">
         <v>387</v>
@@ -14639,10 +14663,10 @@
         <v>0</v>
       </c>
       <c r="G203" s="28">
-        <v>46335</v>
+        <v>46331</v>
       </c>
       <c r="H203" s="28">
-        <v>46335</v>
+        <v>46331</v>
       </c>
       <c r="I203" s="29">
         <f>NETWORKDAYS(G203,H203)</f>
@@ -14683,7 +14707,7 @@
     </row>
     <row r="204" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A204" s="25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B204" s="26" t="s">
         <v>389</v>
@@ -14701,10 +14725,10 @@
         <v>0</v>
       </c>
       <c r="G204" s="28">
-        <v>46335</v>
+        <v>46331</v>
       </c>
       <c r="H204" s="28">
-        <v>46335</v>
+        <v>46331</v>
       </c>
       <c r="I204" s="29">
         <f>NETWORKDAYS(G204,H204)</f>
@@ -14745,7 +14769,7 @@
     </row>
     <row r="205" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A205" s="25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B205" s="26" t="s">
         <v>391</v>
@@ -14763,10 +14787,10 @@
         <v>0</v>
       </c>
       <c r="G205" s="28">
-        <v>46336</v>
+        <v>46332</v>
       </c>
       <c r="H205" s="28">
-        <v>46336</v>
+        <v>46332</v>
       </c>
       <c r="I205" s="29">
         <f>NETWORKDAYS(G205,H205)</f>
@@ -14807,13 +14831,13 @@
     </row>
     <row r="206" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A206" s="25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B206" s="26" t="s">
         <v>393</v>
       </c>
       <c r="C206" s="26" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="D206" s="25" t="s">
         <v>11</v>
@@ -14825,10 +14849,10 @@
         <v>0</v>
       </c>
       <c r="G206" s="28">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="H206" s="28">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="I206" s="29">
         <f>NETWORKDAYS(G206,H206)</f>
@@ -14869,13 +14893,13 @@
     </row>
     <row r="207" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A207" s="25">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B207" s="26" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C207" s="26" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D207" s="25" t="s">
         <v>11</v>
@@ -14887,10 +14911,10 @@
         <v>0</v>
       </c>
       <c r="G207" s="28">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="H207" s="28">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="I207" s="29">
         <f>NETWORKDAYS(G207,H207)</f>
@@ -14931,13 +14955,13 @@
     </row>
     <row r="208" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A208" s="25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B208" s="26" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C208" s="26" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D208" s="25" t="s">
         <v>11</v>
@@ -14949,10 +14973,10 @@
         <v>0</v>
       </c>
       <c r="G208" s="28">
-        <v>46337</v>
+        <v>46335</v>
       </c>
       <c r="H208" s="28">
-        <v>46337</v>
+        <v>46335</v>
       </c>
       <c r="I208" s="29">
         <f>NETWORKDAYS(G208,H208)</f>
@@ -14993,13 +15017,13 @@
     </row>
     <row r="209" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A209" s="25">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B209" s="26" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C209" s="26" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D209" s="25" t="s">
         <v>11</v>
@@ -15011,10 +15035,10 @@
         <v>0</v>
       </c>
       <c r="G209" s="28">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="H209" s="28">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="I209" s="29">
         <f>NETWORKDAYS(G209,H209)</f>
@@ -15055,13 +15079,13 @@
     </row>
     <row r="210" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A210" s="25">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B210" s="26" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C210" s="26" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="D210" s="25" t="s">
         <v>11</v>
@@ -15073,10 +15097,10 @@
         <v>0</v>
       </c>
       <c r="G210" s="28">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="H210" s="28">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="I210" s="29">
         <f>NETWORKDAYS(G210,H210)</f>
@@ -15117,7 +15141,7 @@
     </row>
     <row r="211" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A211" s="25">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B211" s="26" t="s">
         <v>402</v>
@@ -15135,10 +15159,10 @@
         <v>0</v>
       </c>
       <c r="G211" s="28">
-        <v>46338</v>
+        <v>46336</v>
       </c>
       <c r="H211" s="28">
-        <v>46338</v>
+        <v>46336</v>
       </c>
       <c r="I211" s="29">
         <f>NETWORKDAYS(G211,H211)</f>
@@ -15179,7 +15203,7 @@
     </row>
     <row r="212" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A212" s="25">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B212" s="26" t="s">
         <v>404</v>
@@ -15197,10 +15221,10 @@
         <v>0</v>
       </c>
       <c r="G212" s="28">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="H212" s="28">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="I212" s="29">
         <f>NETWORKDAYS(G212,H212)</f>
@@ -15241,7 +15265,7 @@
     </row>
     <row r="213" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A213" s="25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B213" s="26" t="s">
         <v>406</v>
@@ -15259,10 +15283,10 @@
         <v>0</v>
       </c>
       <c r="G213" s="28">
-        <v>46339</v>
+        <v>46337</v>
       </c>
       <c r="H213" s="28">
-        <v>46339</v>
+        <v>46337</v>
       </c>
       <c r="I213" s="29">
         <f>NETWORKDAYS(G213,H213)</f>
@@ -15303,7 +15327,7 @@
     </row>
     <row r="214" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A214" s="25">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B214" s="26" t="s">
         <v>408</v>
@@ -15321,10 +15345,10 @@
         <v>0</v>
       </c>
       <c r="G214" s="28">
-        <v>46339</v>
+        <v>46337</v>
       </c>
       <c r="H214" s="28">
-        <v>46339</v>
+        <v>46337</v>
       </c>
       <c r="I214" s="29">
         <f>NETWORKDAYS(G214,H214)</f>
@@ -15365,7 +15389,7 @@
     </row>
     <row r="215" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A215" s="25">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B215" s="26" t="s">
         <v>410</v>
@@ -15383,10 +15407,10 @@
         <v>0</v>
       </c>
       <c r="G215" s="28">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="H215" s="28">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="I215" s="29">
         <f>NETWORKDAYS(G215,H215)</f>
@@ -15425,75 +15449,71 @@
       <c r="AM215" s="30"/>
       <c r="AN215" s="30"/>
     </row>
-    <row r="216" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A216" s="19" t="s">
+    <row r="216" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A216" s="25">
+        <v>15</v>
+      </c>
+      <c r="B216" s="26" t="s">
         <v>412</v>
       </c>
-      <c r="B216" s="20" t="s">
+      <c r="C216" s="26" t="s">
         <v>413</v>
       </c>
-      <c r="C216" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D216" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E216" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F216" s="22">
-        <f>AVERAGE(F217:F252)</f>
-      </c>
-      <c r="G216" s="23">
-        <f>MIN(G217:G252)</f>
-      </c>
-      <c r="H216" s="23">
-        <f>MAX(H217:H252)</f>
-      </c>
-      <c r="I216" s="19">
+      <c r="D216" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E216" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F216" s="27">
+        <v>0</v>
+      </c>
+      <c r="G216" s="28">
+        <v>46338</v>
+      </c>
+      <c r="H216" s="28">
+        <v>46338</v>
+      </c>
+      <c r="I216" s="29">
         <f>NETWORKDAYS(G216,H216)</f>
       </c>
-      <c r="J216" s="23">
-        <f>IF(COUNT(J217:J252)=0,"",MIN(J217:J252))</f>
-      </c>
-      <c r="K216" s="23">
-        <f>IF(COUNT(K217:K252)=0,"",MAX(K217:K252))</f>
-      </c>
-      <c r="L216" s="19">
+      <c r="J216" s="28"/>
+      <c r="K216" s="28"/>
+      <c r="L216" s="29">
         <f>IF(OR(J216="",K216=""),"",NETWORKDAYS(J216,K216))</f>
       </c>
-      <c r="M216" s="24"/>
-      <c r="N216" s="24"/>
-      <c r="O216" s="24"/>
-      <c r="P216" s="24"/>
-      <c r="Q216" s="24"/>
-      <c r="R216" s="24"/>
-      <c r="S216" s="24"/>
-      <c r="T216" s="24"/>
-      <c r="U216" s="24"/>
-      <c r="V216" s="24"/>
-      <c r="W216" s="24"/>
-      <c r="X216" s="24"/>
-      <c r="Y216" s="24"/>
-      <c r="Z216" s="24"/>
-      <c r="AA216" s="24"/>
-      <c r="AB216" s="24"/>
-      <c r="AC216" s="24"/>
-      <c r="AD216" s="24"/>
-      <c r="AE216" s="24"/>
-      <c r="AF216" s="24"/>
-      <c r="AG216" s="24"/>
-      <c r="AH216" s="24"/>
-      <c r="AI216" s="24"/>
-      <c r="AJ216" s="24"/>
-      <c r="AK216" s="24"/>
-      <c r="AL216" s="24"/>
-      <c r="AM216" s="24"/>
-      <c r="AN216" s="24"/>
+      <c r="M216" s="30"/>
+      <c r="N216" s="30"/>
+      <c r="O216" s="30"/>
+      <c r="P216" s="30"/>
+      <c r="Q216" s="30"/>
+      <c r="R216" s="30"/>
+      <c r="S216" s="30"/>
+      <c r="T216" s="30"/>
+      <c r="U216" s="30"/>
+      <c r="V216" s="30"/>
+      <c r="W216" s="30"/>
+      <c r="X216" s="30"/>
+      <c r="Y216" s="30"/>
+      <c r="Z216" s="30"/>
+      <c r="AA216" s="30"/>
+      <c r="AB216" s="30"/>
+      <c r="AC216" s="30"/>
+      <c r="AD216" s="30"/>
+      <c r="AE216" s="30"/>
+      <c r="AF216" s="30"/>
+      <c r="AG216" s="30"/>
+      <c r="AH216" s="30"/>
+      <c r="AI216" s="30"/>
+      <c r="AJ216" s="30"/>
+      <c r="AK216" s="30"/>
+      <c r="AL216" s="30"/>
+      <c r="AM216" s="30"/>
+      <c r="AN216" s="30"/>
     </row>
     <row r="217" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A217" s="25">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B217" s="26" t="s">
         <v>414</v>
@@ -15502,7 +15522,7 @@
         <v>415</v>
       </c>
       <c r="D217" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E217" s="25" t="s">
         <v>9</v>
@@ -15511,10 +15531,10 @@
         <v>0</v>
       </c>
       <c r="G217" s="28">
-        <v>46342</v>
+        <v>46339</v>
       </c>
       <c r="H217" s="28">
-        <v>46342</v>
+        <v>46339</v>
       </c>
       <c r="I217" s="29">
         <f>NETWORKDAYS(G217,H217)</f>
@@ -15555,7 +15575,7 @@
     </row>
     <row r="218" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A218" s="25">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B218" s="26" t="s">
         <v>416</v>
@@ -15564,7 +15584,7 @@
         <v>417</v>
       </c>
       <c r="D218" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E218" s="25" t="s">
         <v>9</v>
@@ -15573,10 +15593,10 @@
         <v>0</v>
       </c>
       <c r="G218" s="28">
-        <v>46342</v>
+        <v>46339</v>
       </c>
       <c r="H218" s="28">
-        <v>46342</v>
+        <v>46339</v>
       </c>
       <c r="I218" s="29">
         <f>NETWORKDAYS(G218,H218)</f>
@@ -15617,28 +15637,28 @@
     </row>
     <row r="219" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A219" s="25">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B219" s="26" t="s">
         <v>418</v>
       </c>
       <c r="C219" s="26" t="s">
-        <v>360</v>
+        <v>419</v>
       </c>
       <c r="D219" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E219" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F219" s="27">
         <v>0</v>
       </c>
       <c r="G219" s="28">
-        <v>46342</v>
+        <v>46339</v>
       </c>
       <c r="H219" s="28">
-        <v>46342</v>
+        <v>46339</v>
       </c>
       <c r="I219" s="29">
         <f>NETWORKDAYS(G219,H219)</f>
@@ -15677,83 +15697,87 @@
       <c r="AM219" s="30"/>
       <c r="AN219" s="30"/>
     </row>
-    <row r="220" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A220" s="25">
-        <v>4</v>
-      </c>
-      <c r="B220" s="26" t="s">
-        <v>419</v>
-      </c>
-      <c r="C220" s="26" t="s">
+    <row r="220" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A220" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D220" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E220" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F220" s="27">
-        <v>0</v>
-      </c>
-      <c r="G220" s="28">
-        <v>46342</v>
-      </c>
-      <c r="H220" s="28">
-        <v>46342</v>
-      </c>
-      <c r="I220" s="29">
+      <c r="B220" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="C220" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D220" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E220" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F220" s="22">
+        <f>AVERAGE(F221:F256)</f>
+      </c>
+      <c r="G220" s="23">
+        <f>MIN(G221:G256)</f>
+      </c>
+      <c r="H220" s="23">
+        <f>MAX(H221:H256)</f>
+      </c>
+      <c r="I220" s="19">
         <f>NETWORKDAYS(G220,H220)</f>
       </c>
-      <c r="J220" s="28"/>
-      <c r="K220" s="28"/>
-      <c r="L220" s="29">
+      <c r="J220" s="23">
+        <f>IF(COUNT(J221:J256)=0,"",MIN(J221:J256))</f>
+      </c>
+      <c r="K220" s="23">
+        <f>IF(COUNT(K221:K256)=0,"",MAX(K221:K256))</f>
+      </c>
+      <c r="L220" s="19">
         <f>IF(OR(J220="",K220=""),"",NETWORKDAYS(J220,K220))</f>
       </c>
-      <c r="M220" s="30"/>
-      <c r="N220" s="30"/>
-      <c r="O220" s="30"/>
-      <c r="P220" s="30"/>
-      <c r="Q220" s="30"/>
-      <c r="R220" s="30"/>
-      <c r="S220" s="30"/>
-      <c r="T220" s="30"/>
-      <c r="U220" s="30"/>
-      <c r="V220" s="30"/>
-      <c r="W220" s="30"/>
-      <c r="X220" s="30"/>
-      <c r="Y220" s="30"/>
-      <c r="Z220" s="30"/>
-      <c r="AA220" s="30"/>
-      <c r="AB220" s="30"/>
-      <c r="AC220" s="30"/>
-      <c r="AD220" s="30"/>
-      <c r="AE220" s="30"/>
-      <c r="AF220" s="30"/>
-      <c r="AG220" s="30"/>
-      <c r="AH220" s="30"/>
-      <c r="AI220" s="30"/>
-      <c r="AJ220" s="30"/>
-      <c r="AK220" s="30"/>
-      <c r="AL220" s="30"/>
-      <c r="AM220" s="30"/>
-      <c r="AN220" s="30"/>
+      <c r="M220" s="24"/>
+      <c r="N220" s="24"/>
+      <c r="O220" s="24"/>
+      <c r="P220" s="24"/>
+      <c r="Q220" s="24"/>
+      <c r="R220" s="24"/>
+      <c r="S220" s="24"/>
+      <c r="T220" s="24"/>
+      <c r="U220" s="24"/>
+      <c r="V220" s="24"/>
+      <c r="W220" s="24"/>
+      <c r="X220" s="24"/>
+      <c r="Y220" s="24"/>
+      <c r="Z220" s="24"/>
+      <c r="AA220" s="24"/>
+      <c r="AB220" s="24"/>
+      <c r="AC220" s="24"/>
+      <c r="AD220" s="24"/>
+      <c r="AE220" s="24"/>
+      <c r="AF220" s="24"/>
+      <c r="AG220" s="24"/>
+      <c r="AH220" s="24"/>
+      <c r="AI220" s="24"/>
+      <c r="AJ220" s="24"/>
+      <c r="AK220" s="24"/>
+      <c r="AL220" s="24"/>
+      <c r="AM220" s="24"/>
+      <c r="AN220" s="24"/>
     </row>
     <row r="221" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A221" s="25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B221" s="26" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C221" s="26" t="s">
-        <v>360</v>
+        <v>423</v>
       </c>
       <c r="D221" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E221" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F221" s="27">
         <v>0</v>
@@ -15803,19 +15827,19 @@
     </row>
     <row r="222" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A222" s="25">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B222" s="26" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C222" s="26" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D222" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E222" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F222" s="27">
         <v>0</v>
@@ -15865,19 +15889,19 @@
     </row>
     <row r="223" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A223" s="25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B223" s="26" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C223" s="26" t="s">
-        <v>425</v>
+        <v>366</v>
       </c>
       <c r="D223" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E223" s="25" t="s">
         <v>11</v>
-      </c>
-      <c r="E223" s="25" t="s">
-        <v>9</v>
       </c>
       <c r="F223" s="27">
         <v>0</v>
@@ -15927,19 +15951,19 @@
     </row>
     <row r="224" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A224" s="25">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B224" s="26" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C224" s="26" t="s">
-        <v>360</v>
+        <v>428</v>
       </c>
       <c r="D224" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224" s="25" t="s">
         <v>11</v>
-      </c>
-      <c r="E224" s="25" t="s">
-        <v>9</v>
       </c>
       <c r="F224" s="27">
         <v>0</v>
@@ -15989,28 +16013,28 @@
     </row>
     <row r="225" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A225" s="25">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B225" s="26" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C225" s="26" t="s">
-        <v>428</v>
+        <v>366</v>
       </c>
       <c r="D225" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E225" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E225" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="F225" s="27">
         <v>0</v>
       </c>
       <c r="G225" s="28">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="H225" s="28">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="I225" s="29">
         <f>NETWORKDAYS(G225,H225)</f>
@@ -16051,28 +16075,28 @@
     </row>
     <row r="226" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A226" s="25">
+        <v>6</v>
+      </c>
+      <c r="B226" s="26" t="s">
+        <v>430</v>
+      </c>
+      <c r="C226" s="26" t="s">
+        <v>431</v>
+      </c>
+      <c r="D226" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B226" s="26" t="s">
-        <v>429</v>
-      </c>
-      <c r="C226" s="26" t="s">
-        <v>430</v>
-      </c>
-      <c r="D226" s="25" t="s">
+      <c r="E226" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E226" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="F226" s="27">
         <v>0</v>
       </c>
       <c r="G226" s="28">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="H226" s="28">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="I226" s="29">
         <f>NETWORKDAYS(G226,H226)</f>
@@ -16113,28 +16137,28 @@
     </row>
     <row r="227" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A227" s="25">
+        <v>7</v>
+      </c>
+      <c r="B227" s="26" t="s">
+        <v>432</v>
+      </c>
+      <c r="C227" s="26" t="s">
+        <v>433</v>
+      </c>
+      <c r="D227" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B227" s="26" t="s">
-        <v>431</v>
-      </c>
-      <c r="C227" s="26" t="s">
-        <v>432</v>
-      </c>
-      <c r="D227" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="E227" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F227" s="27">
         <v>0</v>
       </c>
       <c r="G227" s="28">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="H227" s="28">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="I227" s="29">
         <f>NETWORKDAYS(G227,H227)</f>
@@ -16175,28 +16199,28 @@
     </row>
     <row r="228" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A228" s="25">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B228" s="26" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C228" s="26" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="D228" s="25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E228" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F228" s="27">
         <v>0</v>
       </c>
       <c r="G228" s="28">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="H228" s="28">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="I228" s="29">
         <f>NETWORKDAYS(G228,H228)</f>
@@ -16237,7 +16261,7 @@
     </row>
     <row r="229" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A229" s="25">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B229" s="26" t="s">
         <v>435</v>
@@ -16246,10 +16270,10 @@
         <v>436</v>
       </c>
       <c r="D229" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E229" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F229" s="27">
         <v>0</v>
@@ -16299,7 +16323,7 @@
     </row>
     <row r="230" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A230" s="25">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B230" s="26" t="s">
         <v>437</v>
@@ -16308,7 +16332,7 @@
         <v>438</v>
       </c>
       <c r="D230" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E230" s="25" t="s">
         <v>9</v>
@@ -16361,7 +16385,7 @@
     </row>
     <row r="231" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A231" s="25">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B231" s="26" t="s">
         <v>439</v>
@@ -16370,10 +16394,10 @@
         <v>440</v>
       </c>
       <c r="D231" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E231" s="25" t="s">
         <v>11</v>
-      </c>
-      <c r="E231" s="25" t="s">
-        <v>9</v>
       </c>
       <c r="F231" s="27">
         <v>0</v>
@@ -16423,7 +16447,7 @@
     </row>
     <row r="232" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A232" s="25">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B232" s="26" t="s">
         <v>441</v>
@@ -16432,19 +16456,19 @@
         <v>442</v>
       </c>
       <c r="D232" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E232" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E232" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="F232" s="27">
         <v>0</v>
       </c>
       <c r="G232" s="28">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="H232" s="28">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="I232" s="29">
         <f>NETWORKDAYS(G232,H232)</f>
@@ -16485,7 +16509,7 @@
     </row>
     <row r="233" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A233" s="25">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B233" s="26" t="s">
         <v>443</v>
@@ -16494,19 +16518,19 @@
         <v>444</v>
       </c>
       <c r="D233" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E233" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E233" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="F233" s="27">
         <v>0</v>
       </c>
       <c r="G233" s="28">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="H233" s="28">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="I233" s="29">
         <f>NETWORKDAYS(G233,H233)</f>
@@ -16547,28 +16571,28 @@
     </row>
     <row r="234" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A234" s="25">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B234" s="26" t="s">
         <v>445</v>
       </c>
       <c r="C234" s="26" t="s">
-        <v>260</v>
+        <v>446</v>
       </c>
       <c r="D234" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E234" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F234" s="27">
         <v>0</v>
       </c>
       <c r="G234" s="28">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="H234" s="28">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="I234" s="29">
         <f>NETWORKDAYS(G234,H234)</f>
@@ -16609,28 +16633,28 @@
     </row>
     <row r="235" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A235" s="25">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B235" s="26" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C235" s="26" t="s">
-        <v>362</v>
+        <v>448</v>
       </c>
       <c r="D235" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E235" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F235" s="27">
         <v>0</v>
       </c>
       <c r="G235" s="28">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="H235" s="28">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="I235" s="29">
         <f>NETWORKDAYS(G235,H235)</f>
@@ -16671,19 +16695,19 @@
     </row>
     <row r="236" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A236" s="25">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B236" s="26" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C236" s="26" t="s">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="D236" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E236" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F236" s="27">
         <v>0</v>
@@ -16733,19 +16757,19 @@
     </row>
     <row r="237" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A237" s="25">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B237" s="26" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C237" s="26" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D237" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E237" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F237" s="27">
         <v>0</v>
@@ -16795,19 +16819,19 @@
     </row>
     <row r="238" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A238" s="25">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B238" s="26" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C238" s="26" t="s">
-        <v>451</v>
+        <v>242</v>
       </c>
       <c r="D238" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E238" s="25" t="s">
         <v>11</v>
-      </c>
-      <c r="E238" s="25" t="s">
-        <v>9</v>
       </c>
       <c r="F238" s="27">
         <v>0</v>
@@ -16857,19 +16881,19 @@
     </row>
     <row r="239" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A239" s="25">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B239" s="26" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C239" s="26" t="s">
-        <v>453</v>
+        <v>368</v>
       </c>
       <c r="D239" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E239" s="25" t="s">
         <v>11</v>
-      </c>
-      <c r="E239" s="25" t="s">
-        <v>9</v>
       </c>
       <c r="F239" s="27">
         <v>0</v>
@@ -16919,28 +16943,28 @@
     </row>
     <row r="240" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A240" s="25">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B240" s="26" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C240" s="26" t="s">
-        <v>455</v>
+        <v>366</v>
       </c>
       <c r="D240" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E240" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E240" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="F240" s="27">
         <v>0</v>
       </c>
       <c r="G240" s="28">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="H240" s="28">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="I240" s="29">
         <f>NETWORKDAYS(G240,H240)</f>
@@ -16981,7 +17005,7 @@
     </row>
     <row r="241" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A241" s="25">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B241" s="26" t="s">
         <v>456</v>
@@ -16990,19 +17014,19 @@
         <v>457</v>
       </c>
       <c r="D241" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E241" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E241" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="F241" s="27">
         <v>0</v>
       </c>
       <c r="G241" s="28">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="H241" s="28">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="I241" s="29">
         <f>NETWORKDAYS(G241,H241)</f>
@@ -17043,7 +17067,7 @@
     </row>
     <row r="242" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A242" s="25">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B242" s="26" t="s">
         <v>458</v>
@@ -17052,19 +17076,19 @@
         <v>459</v>
       </c>
       <c r="D242" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E242" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F242" s="27">
         <v>0</v>
       </c>
       <c r="G242" s="28">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="H242" s="28">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="I242" s="29">
         <f>NETWORKDAYS(G242,H242)</f>
@@ -17105,7 +17129,7 @@
     </row>
     <row r="243" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A243" s="25">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B243" s="26" t="s">
         <v>460</v>
@@ -17114,19 +17138,19 @@
         <v>461</v>
       </c>
       <c r="D243" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E243" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F243" s="27">
         <v>0</v>
       </c>
       <c r="G243" s="28">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="H243" s="28">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="I243" s="29">
         <f>NETWORKDAYS(G243,H243)</f>
@@ -17167,19 +17191,19 @@
     </row>
     <row r="244" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A244" s="25">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B244" s="26" t="s">
         <v>462</v>
       </c>
       <c r="C244" s="26" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D244" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E244" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F244" s="27">
         <v>0</v>
@@ -17229,19 +17253,19 @@
     </row>
     <row r="245" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A245" s="25">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B245" s="26" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C245" s="26" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D245" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E245" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F245" s="27">
         <v>0</v>
@@ -17291,19 +17315,19 @@
     </row>
     <row r="246" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A246" s="25">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B246" s="26" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C246" s="26" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D246" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E246" s="25" t="s">
         <v>11</v>
-      </c>
-      <c r="E246" s="25" t="s">
-        <v>9</v>
       </c>
       <c r="F246" s="27">
         <v>0</v>
@@ -17353,19 +17377,19 @@
     </row>
     <row r="247" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A247" s="25">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B247" s="26" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C247" s="26" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D247" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E247" s="25" t="s">
         <v>11</v>
-      </c>
-      <c r="E247" s="25" t="s">
-        <v>9</v>
       </c>
       <c r="F247" s="27">
         <v>0</v>
@@ -17415,28 +17439,28 @@
     </row>
     <row r="248" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A248" s="25">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B248" s="26" t="s">
+        <v>470</v>
+      </c>
+      <c r="C248" s="26" t="s">
         <v>467</v>
       </c>
-      <c r="C248" s="26" t="s">
-        <v>468</v>
-      </c>
       <c r="D248" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E248" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E248" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="F248" s="27">
         <v>0</v>
       </c>
       <c r="G248" s="28">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="H248" s="28">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="I248" s="29">
         <f>NETWORKDAYS(G248,H248)</f>
@@ -17477,28 +17501,28 @@
     </row>
     <row r="249" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A249" s="25">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B249" s="26" t="s">
+        <v>471</v>
+      </c>
+      <c r="C249" s="26" t="s">
         <v>469</v>
       </c>
-      <c r="C249" s="26" t="s">
-        <v>470</v>
-      </c>
       <c r="D249" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E249" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E249" s="25" t="s">
-        <v>9</v>
-      </c>
       <c r="F249" s="27">
         <v>0</v>
       </c>
       <c r="G249" s="28">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="H249" s="28">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="I249" s="29">
         <f>NETWORKDAYS(G249,H249)</f>
@@ -17539,28 +17563,28 @@
     </row>
     <row r="250" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A250" s="25">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B250" s="26" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C250" s="26" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="D250" s="25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E250" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F250" s="27">
         <v>0</v>
       </c>
       <c r="G250" s="28">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="H250" s="28">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="I250" s="29">
         <f>NETWORKDAYS(G250,H250)</f>
@@ -17601,28 +17625,28 @@
     </row>
     <row r="251" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A251" s="25">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B251" s="26" t="s">
         <v>473</v>
       </c>
       <c r="C251" s="26" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D251" s="25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E251" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F251" s="27">
         <v>0</v>
       </c>
       <c r="G251" s="28">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="H251" s="28">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="I251" s="29">
         <f>NETWORKDAYS(G251,H251)</f>
@@ -17663,16 +17687,16 @@
     </row>
     <row r="252" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A252" s="25">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B252" s="26" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C252" s="26" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D252" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E252" s="25" t="s">
         <v>9</v>
@@ -17723,12 +17747,260 @@
       <c r="AM252" s="30"/>
       <c r="AN252" s="30"/>
     </row>
+    <row r="253" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A253" s="25">
+        <v>33</v>
+      </c>
+      <c r="B253" s="26" t="s">
+        <v>477</v>
+      </c>
+      <c r="C253" s="26" t="s">
+        <v>478</v>
+      </c>
+      <c r="D253" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E253" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F253" s="27">
+        <v>0</v>
+      </c>
+      <c r="G253" s="28">
+        <v>46346</v>
+      </c>
+      <c r="H253" s="28">
+        <v>46346</v>
+      </c>
+      <c r="I253" s="29">
+        <f>NETWORKDAYS(G253,H253)</f>
+      </c>
+      <c r="J253" s="28"/>
+      <c r="K253" s="28"/>
+      <c r="L253" s="29">
+        <f>IF(OR(J253="",K253=""),"",NETWORKDAYS(J253,K253))</f>
+      </c>
+      <c r="M253" s="30"/>
+      <c r="N253" s="30"/>
+      <c r="O253" s="30"/>
+      <c r="P253" s="30"/>
+      <c r="Q253" s="30"/>
+      <c r="R253" s="30"/>
+      <c r="S253" s="30"/>
+      <c r="T253" s="30"/>
+      <c r="U253" s="30"/>
+      <c r="V253" s="30"/>
+      <c r="W253" s="30"/>
+      <c r="X253" s="30"/>
+      <c r="Y253" s="30"/>
+      <c r="Z253" s="30"/>
+      <c r="AA253" s="30"/>
+      <c r="AB253" s="30"/>
+      <c r="AC253" s="30"/>
+      <c r="AD253" s="30"/>
+      <c r="AE253" s="30"/>
+      <c r="AF253" s="30"/>
+      <c r="AG253" s="30"/>
+      <c r="AH253" s="30"/>
+      <c r="AI253" s="30"/>
+      <c r="AJ253" s="30"/>
+      <c r="AK253" s="30"/>
+      <c r="AL253" s="30"/>
+      <c r="AM253" s="30"/>
+      <c r="AN253" s="30"/>
+    </row>
+    <row r="254" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A254" s="25">
+        <v>34</v>
+      </c>
+      <c r="B254" s="26" t="s">
+        <v>479</v>
+      </c>
+      <c r="C254" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="D254" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E254" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F254" s="27">
+        <v>0</v>
+      </c>
+      <c r="G254" s="28">
+        <v>46346</v>
+      </c>
+      <c r="H254" s="28">
+        <v>46346</v>
+      </c>
+      <c r="I254" s="29">
+        <f>NETWORKDAYS(G254,H254)</f>
+      </c>
+      <c r="J254" s="28"/>
+      <c r="K254" s="28"/>
+      <c r="L254" s="29">
+        <f>IF(OR(J254="",K254=""),"",NETWORKDAYS(J254,K254))</f>
+      </c>
+      <c r="M254" s="30"/>
+      <c r="N254" s="30"/>
+      <c r="O254" s="30"/>
+      <c r="P254" s="30"/>
+      <c r="Q254" s="30"/>
+      <c r="R254" s="30"/>
+      <c r="S254" s="30"/>
+      <c r="T254" s="30"/>
+      <c r="U254" s="30"/>
+      <c r="V254" s="30"/>
+      <c r="W254" s="30"/>
+      <c r="X254" s="30"/>
+      <c r="Y254" s="30"/>
+      <c r="Z254" s="30"/>
+      <c r="AA254" s="30"/>
+      <c r="AB254" s="30"/>
+      <c r="AC254" s="30"/>
+      <c r="AD254" s="30"/>
+      <c r="AE254" s="30"/>
+      <c r="AF254" s="30"/>
+      <c r="AG254" s="30"/>
+      <c r="AH254" s="30"/>
+      <c r="AI254" s="30"/>
+      <c r="AJ254" s="30"/>
+      <c r="AK254" s="30"/>
+      <c r="AL254" s="30"/>
+      <c r="AM254" s="30"/>
+      <c r="AN254" s="30"/>
+    </row>
+    <row r="255" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A255" s="25">
+        <v>35</v>
+      </c>
+      <c r="B255" s="26" t="s">
+        <v>481</v>
+      </c>
+      <c r="C255" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="D255" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E255" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F255" s="27">
+        <v>0</v>
+      </c>
+      <c r="G255" s="28">
+        <v>46346</v>
+      </c>
+      <c r="H255" s="28">
+        <v>46346</v>
+      </c>
+      <c r="I255" s="29">
+        <f>NETWORKDAYS(G255,H255)</f>
+      </c>
+      <c r="J255" s="28"/>
+      <c r="K255" s="28"/>
+      <c r="L255" s="29">
+        <f>IF(OR(J255="",K255=""),"",NETWORKDAYS(J255,K255))</f>
+      </c>
+      <c r="M255" s="30"/>
+      <c r="N255" s="30"/>
+      <c r="O255" s="30"/>
+      <c r="P255" s="30"/>
+      <c r="Q255" s="30"/>
+      <c r="R255" s="30"/>
+      <c r="S255" s="30"/>
+      <c r="T255" s="30"/>
+      <c r="U255" s="30"/>
+      <c r="V255" s="30"/>
+      <c r="W255" s="30"/>
+      <c r="X255" s="30"/>
+      <c r="Y255" s="30"/>
+      <c r="Z255" s="30"/>
+      <c r="AA255" s="30"/>
+      <c r="AB255" s="30"/>
+      <c r="AC255" s="30"/>
+      <c r="AD255" s="30"/>
+      <c r="AE255" s="30"/>
+      <c r="AF255" s="30"/>
+      <c r="AG255" s="30"/>
+      <c r="AH255" s="30"/>
+      <c r="AI255" s="30"/>
+      <c r="AJ255" s="30"/>
+      <c r="AK255" s="30"/>
+      <c r="AL255" s="30"/>
+      <c r="AM255" s="30"/>
+      <c r="AN255" s="30"/>
+    </row>
+    <row r="256" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A256" s="25">
+        <v>36</v>
+      </c>
+      <c r="B256" s="26" t="s">
+        <v>482</v>
+      </c>
+      <c r="C256" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="D256" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E256" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F256" s="27">
+        <v>0</v>
+      </c>
+      <c r="G256" s="28">
+        <v>46346</v>
+      </c>
+      <c r="H256" s="28">
+        <v>46346</v>
+      </c>
+      <c r="I256" s="29">
+        <f>NETWORKDAYS(G256,H256)</f>
+      </c>
+      <c r="J256" s="28"/>
+      <c r="K256" s="28"/>
+      <c r="L256" s="29">
+        <f>IF(OR(J256="",K256=""),"",NETWORKDAYS(J256,K256))</f>
+      </c>
+      <c r="M256" s="30"/>
+      <c r="N256" s="30"/>
+      <c r="O256" s="30"/>
+      <c r="P256" s="30"/>
+      <c r="Q256" s="30"/>
+      <c r="R256" s="30"/>
+      <c r="S256" s="30"/>
+      <c r="T256" s="30"/>
+      <c r="U256" s="30"/>
+      <c r="V256" s="30"/>
+      <c r="W256" s="30"/>
+      <c r="X256" s="30"/>
+      <c r="Y256" s="30"/>
+      <c r="Z256" s="30"/>
+      <c r="AA256" s="30"/>
+      <c r="AB256" s="30"/>
+      <c r="AC256" s="30"/>
+      <c r="AD256" s="30"/>
+      <c r="AE256" s="30"/>
+      <c r="AF256" s="30"/>
+      <c r="AG256" s="30"/>
+      <c r="AH256" s="30"/>
+      <c r="AI256" s="30"/>
+      <c r="AJ256" s="30"/>
+      <c r="AK256" s="30"/>
+      <c r="AL256" s="30"/>
+      <c r="AM256" s="30"/>
+      <c r="AN256" s="30"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A7:L252"/>
+  <autoFilter ref="A7:L256"/>
   <mergeCells count="1">
     <mergeCell ref="M4:P4"/>
   </mergeCells>
-  <conditionalFormatting sqref="M9:AN252">
+  <conditionalFormatting sqref="M9:AN256">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>M$5=TODAY()</formula>
     </cfRule>
@@ -17778,7 +18050,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -17790,33 +18062,33 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="D2" s="38" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E2" s="38" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F2" s="38" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="H2" s="38" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -17831,16 +18103,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="D4" s="41" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="F4" s="41" t="s">
         <v>28</v>
@@ -17849,7 +18121,7 @@
         <v>28</v>
       </c>
       <c r="H4" s="41" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" ht="50" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17857,16 +18129,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="F5" s="41" t="s">
         <v>28</v>
@@ -17875,7 +18147,7 @@
         <v>28</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" ht="50" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17883,16 +18155,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="41" t="s">
+        <v>502</v>
+      </c>
+      <c r="C6" s="41" t="s">
         <v>494</v>
       </c>
-      <c r="C6" s="41" t="s">
-        <v>486</v>
-      </c>
       <c r="D6" s="41" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="F6" s="41" t="s">
         <v>28</v>
@@ -17901,7 +18173,7 @@
         <v>28</v>
       </c>
       <c r="H6" s="41" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17909,16 +18181,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="F7" s="41" t="s">
         <v>28</v>
@@ -17927,12 +18199,12 @@
         <v>28</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="39" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="B9" s="39"/>
       <c r="C9" s="39"/>
@@ -17947,16 +18219,16 @@
         <v>1</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="F10" s="41" t="s">
         <v>28</v>
